--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1255,7 +1255,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,6 +791,9 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
+    <t>final</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
   </si>
   <si>
@@ -809,7 +812,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1242: fixed value = final</t>
+    <t>1242: fixed value = #final</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -940,6 +943,9 @@
     <t>Need to refer to a particular code in the system.</t>
   </si>
   <si>
+    <t>social-history</t>
+  </si>
+  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -949,7 +955,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>1243: fixed value = social-history</t>
+    <t>1243: fixed value = #social-history</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -4979,7 +4985,7 @@
         <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>84</v>
@@ -4998,7 +5004,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -5031,25 +5037,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -5057,10 +5063,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5086,16 +5092,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5123,16 +5129,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5142,7 +5148,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5172,10 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
@@ -5183,10 +5189,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5307,10 +5313,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5433,10 +5439,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5459,19 +5465,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5520,7 +5526,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5541,10 +5547,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5561,10 +5567,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5685,10 +5691,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5811,10 +5817,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5840,16 +5846,16 @@
         <v>108</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5898,7 +5904,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5919,10 +5925,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5939,10 +5945,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5968,13 +5974,13 @@
         <v>161</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6024,7 +6030,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6045,10 +6051,10 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>84</v>
@@ -6065,10 +6071,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6094,14 +6100,14 @@
         <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6111,7 +6117,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6150,7 +6156,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6171,10 +6177,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6183,7 +6189,7 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6191,10 +6197,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6220,14 +6226,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6276,7 +6282,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6297,10 +6303,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6317,10 +6323,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6343,19 +6349,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6404,7 +6410,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6425,10 +6431,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6445,10 +6451,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6474,16 +6480,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6532,7 +6538,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6553,10 +6559,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6573,13 +6579,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6604,16 +6610,16 @@
         <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6623,7 +6629,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6641,10 +6647,10 @@
         <v>118</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6662,7 +6668,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6686,10 +6692,10 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6703,14 +6709,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6732,16 +6738,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6770,7 +6776,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6788,7 +6794,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>94</v>
@@ -6803,22 +6809,22 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6829,10 +6835,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6855,19 +6861,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6916,7 +6922,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6931,25 +6937,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6957,10 +6963,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6983,16 +6989,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7042,7 +7048,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7063,13 +7069,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7083,14 +7089,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7109,19 +7115,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7170,7 +7176,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7185,40 +7191,40 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7237,19 +7243,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7286,17 +7292,17 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7311,19 +7317,19 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7337,16 +7343,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7365,19 +7371,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7426,7 +7432,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7441,36 +7447,36 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7493,16 +7499,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7552,7 +7558,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7573,13 +7579,13 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
@@ -7593,10 +7599,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7619,17 +7625,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7678,7 +7684,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7693,25 +7699,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7719,10 +7725,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7748,16 +7754,16 @@
         <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7794,17 +7800,17 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7813,7 +7819,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7822,19 +7828,19 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7845,13 +7851,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -7876,16 +7882,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7914,7 +7920,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7932,7 +7938,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7941,7 +7947,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7950,22 +7956,22 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>84</v>
@@ -7973,10 +7979,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8002,16 +8008,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8039,10 +8045,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8060,7 +8066,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8069,7 +8075,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8084,7 +8090,7 @@
         <v>137</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8101,14 +8107,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8130,16 +8136,16 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8167,10 +8173,10 @@
         <v>188</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8188,7 +8194,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8206,19 +8212,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8229,10 +8235,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8255,19 +8261,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8316,7 +8322,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8337,10 +8343,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8357,10 +8363,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8481,10 +8487,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8607,10 +8613,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8633,16 +8639,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8692,7 +8698,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8716,7 +8722,7 @@
         <v>137</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8733,10 +8739,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8759,13 +8765,13 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8816,7 +8822,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8840,7 +8846,7 @@
         <v>137</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8857,10 +8863,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8883,13 +8889,13 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8940,7 +8946,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>94</v>
@@ -8964,7 +8970,7 @@
         <v>137</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8973,18 +8979,18 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9010,13 +9016,13 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9042,13 +9048,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9066,7 +9072,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9084,19 +9090,19 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9107,10 +9113,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9136,16 +9142,16 @@
         <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9170,13 +9176,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9194,7 +9200,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9215,10 +9221,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9235,10 +9241,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9261,16 +9267,16 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9320,7 +9326,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9338,19 +9344,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9361,10 +9367,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9387,16 +9393,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9446,7 +9452,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9464,19 +9470,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9487,10 +9493,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9513,19 +9519,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9574,7 +9580,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9586,7 +9592,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9595,10 +9601,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9615,10 +9621,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9739,10 +9745,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9865,14 +9871,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9894,10 +9900,10 @@
         <v>140</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>143</v>
@@ -9952,7 +9958,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9993,10 +9999,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10019,13 +10025,13 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10076,7 +10082,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10085,7 +10091,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10097,10 +10103,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10117,10 +10123,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10143,13 +10149,13 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -10200,7 +10206,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10209,7 +10215,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10221,10 +10227,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10241,10 +10247,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10270,16 +10276,16 @@
         <v>183</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10307,10 +10313,10 @@
         <v>118</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10328,7 +10334,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10346,13 +10352,13 @@
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10369,10 +10375,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10398,16 +10404,16 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10432,13 +10438,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10456,7 +10462,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10474,13 +10480,13 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10497,10 +10503,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10523,17 +10529,17 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10582,7 +10588,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10606,7 +10612,7 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10623,10 +10629,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10652,10 +10658,10 @@
         <v>161</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10706,7 +10712,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10727,10 +10733,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10747,10 +10753,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10773,16 +10779,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10832,7 +10838,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10853,10 +10859,10 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -10873,10 +10879,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10899,16 +10905,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10958,7 +10964,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10979,10 +10985,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -10999,10 +11005,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11025,19 +11031,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11086,7 +11092,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11107,10 +11113,10 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
@@ -11127,10 +11133,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11251,10 +11257,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11377,14 +11383,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11406,10 +11412,10 @@
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>143</v>
@@ -11464,7 +11470,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11505,10 +11511,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11534,16 +11540,16 @@
         <v>183</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -11568,13 +11574,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11592,7 +11598,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>94</v>
@@ -11610,16 +11616,16 @@
         <v>84</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -11633,10 +11639,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11659,19 +11665,19 @@
         <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -11720,7 +11726,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11738,19 +11744,19 @@
         <v>84</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -11761,10 +11767,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11790,16 +11796,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11827,10 +11833,10 @@
         <v>188</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11848,7 +11854,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -11857,7 +11863,7 @@
         <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>106</v>
@@ -11872,7 +11878,7 @@
         <v>137</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>84</v>
@@ -11889,14 +11895,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11918,16 +11924,16 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -11955,10 +11961,10 @@
         <v>188</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -11976,7 +11982,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -11994,19 +12000,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12017,10 +12023,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12046,16 +12052,16 @@
         <v>85</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12104,7 +12110,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12125,10 +12131,10 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="570">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -828,213 +828,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>social-history</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>1243: fixed value = #social-history</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.category:SocialHistory</t>
-  </si>
-  <si>
-    <t>SocialHistory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1045,6 +838,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>1243: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#social-history</t>
+  </si>
+  <si>
+    <t>Observation.category:SocialHistory</t>
+  </si>
+  <si>
+    <t>SocialHistory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -1083,6 +901,70 @@
   </si>
   <si>
     <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>1244: transform using http://loinc.org#72166-2 on HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
+  </si>
+  <si>
+    <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -2231,7 +2113,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR78"/>
+  <dimension ref="A1:AR71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
@@ -2275,8 +2157,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="101.90625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="109.28515625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="49.95703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5111,7 +4993,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5129,16 +5011,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5172,16 +5054,16 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5189,24 +5071,26 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5215,16 +5099,20 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5233,7 +5121,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5248,13 +5136,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5272,19 +5160,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -5296,10 +5184,10 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5313,44 +5201,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>141</v>
+        <v>273</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>274</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>275</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
       </c>
@@ -5374,61 +5264,59 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5439,10 +5327,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5453,7 +5341,7 @@
         <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>84</v>
@@ -5462,23 +5350,19 @@
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>270</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5526,19 +5410,19 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>84</v>
@@ -5547,10 +5431,10 @@
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>165</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>84</v>
@@ -5567,21 +5451,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -5593,15 +5477,17 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5638,31 +5524,31 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5691,14 +5577,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5708,27 +5594,29 @@
         <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -5764,19 +5652,19 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>292</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5788,7 +5676,7 @@
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>84</v>
@@ -5797,10 +5685,10 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>84</v>
@@ -5809,18 +5697,18 @@
         <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5843,19 +5731,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5904,7 +5792,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5925,10 +5813,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5945,10 +5833,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5956,13 +5844,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -5971,18 +5859,20 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6030,7 +5920,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6045,25 +5935,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>311</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6071,10 +5961,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6085,10 +5975,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6097,18 +5987,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6117,7 +6007,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6156,13 +6046,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6177,19 +6067,19 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>84</v>
+        <v>314</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6197,14 +6087,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6214,7 +6104,7 @@
         <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6223,17 +6113,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6282,7 +6174,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6297,44 +6189,44 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>333</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>94</v>
@@ -6349,19 +6241,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6398,19 +6290,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6425,19 +6315,19 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>84</v>
@@ -6451,24 +6341,26 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6477,19 +6369,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>161</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6538,7 +6430,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6553,74 +6445,70 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>327</v>
+        <v>346</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>351</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>353</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6629,7 +6517,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>330</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6644,13 +6532,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -6668,13 +6556,13 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>257</v>
+        <v>352</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
@@ -6689,13 +6577,13 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>265</v>
+        <v>358</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>266</v>
+        <v>359</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -6709,21 +6597,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>332</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>95</v>
@@ -6735,19 +6623,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>183</v>
+        <v>361</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6772,11 +6658,13 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -6794,13 +6682,13 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
@@ -6809,25 +6697,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6835,10 +6723,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6852,7 +6740,7 @@
         <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
@@ -6861,19 +6749,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>345</v>
+        <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6910,19 +6798,17 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>370</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6931,31 +6817,31 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6963,24 +6849,26 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>84</v>
@@ -6989,18 +6877,20 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>356</v>
+        <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>382</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7024,13 +6914,11 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>383</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -7048,16 +6936,16 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -7066,22 +6954,22 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>376</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>84</v>
+        <v>384</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7089,14 +6977,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7106,28 +6994,28 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7152,13 +7040,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7176,7 +7064,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7185,53 +7073,53 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>369</v>
+        <v>137</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>372</v>
+        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -7240,22 +7128,22 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>379</v>
+        <v>398</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7280,35 +7168,37 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>382</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>84</v>
@@ -7317,22 +7207,22 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>403</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>404</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7343,47 +7233,45 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>388</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>408</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>379</v>
+        <v>410</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>380</v>
+        <v>411</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7432,13 +7320,13 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>84</v>
@@ -7447,36 +7335,36 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>390</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7496,20 +7384,18 @@
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>392</v>
+        <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>393</v>
+        <v>162</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>395</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
@@ -7558,7 +7444,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>391</v>
+        <v>164</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7570,7 +7456,7 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>84</v>
@@ -7579,13 +7465,13 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>397</v>
+        <v>165</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
@@ -7599,14 +7485,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7616,27 +7502,27 @@
         <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7672,19 +7558,19 @@
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>399</v>
+        <v>171</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7696,28 +7582,28 @@
         <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>406</v>
+        <v>165</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7725,10 +7611,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7736,7 +7622,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>94</v>
@@ -7751,20 +7637,18 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>417</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7800,17 +7684,19 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>382</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7819,7 +7705,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7828,19 +7714,19 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>416</v>
+        <v>137</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7851,26 +7737,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
@@ -7879,20 +7763,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>337</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7916,11 +7796,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>422</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7938,7 +7820,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7947,7 +7829,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7956,22 +7838,22 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>416</v>
+        <v>137</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>84</v>
@@ -7979,10 +7861,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7990,35 +7872,31 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>183</v>
+        <v>429</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8042,13 +7920,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8066,16 +7944,16 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8090,7 +7968,7 @@
         <v>137</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8099,29 +7977,29 @@
         <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8136,17 +8014,15 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>439</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8170,13 +8046,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>188</v>
+        <v>440</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8194,13 +8070,13 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
@@ -8212,19 +8088,19 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8235,10 +8111,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8249,7 +8125,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>84</v>
@@ -8261,19 +8137,19 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>446</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8298,13 +8174,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8322,13 +8198,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8343,10 +8219,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8363,10 +8239,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8389,15 +8265,17 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>161</v>
+        <v>457</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>162</v>
+        <v>458</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8446,7 +8324,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8458,25 +8336,25 @@
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>165</v>
+        <v>463</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8487,21 +8365,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>84</v>
@@ -8513,16 +8391,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>140</v>
+        <v>466</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>141</v>
+        <v>467</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>167</v>
+        <v>468</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>143</v>
+        <v>469</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8560,49 +8438,49 @@
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>171</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>165</v>
+        <v>472</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>84</v>
+        <v>473</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8613,10 +8491,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8627,7 +8505,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8636,21 +8514,23 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8698,19 +8578,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>480</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8719,10 +8599,10 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>137</v>
+        <v>481</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -8739,10 +8619,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8762,16 +8642,16 @@
         <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>162</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
+        <v>163</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8822,7 +8702,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>465</v>
+        <v>164</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8834,7 +8714,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8843,10 +8723,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>466</v>
+        <v>165</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -8863,41 +8743,43 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>468</v>
+        <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>469</v>
+        <v>141</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -8946,19 +8828,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>171</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8967,10 +8849,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>472</v>
+        <v>165</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8979,52 +8861,54 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>486</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9048,13 +8932,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>481</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9072,37 +8956,37 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>483</v>
+        <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>484</v>
+        <v>137</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9113,10 +8997,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9139,20 +9023,16 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>491</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9176,13 +9056,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>491</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9200,7 +9080,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9209,7 +9089,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9221,10 +9101,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9241,10 +9121,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9267,17 +9147,15 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N56" t="s" s="2">
         <v>499</v>
       </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9326,7 +9204,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9335,7 +9213,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9344,19 +9222,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AM56" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>502</v>
-      </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9367,10 +9245,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9393,18 +9271,20 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O57" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9428,13 +9308,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>84</v>
+        <v>506</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>84</v>
+        <v>507</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9452,7 +9332,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9470,19 +9350,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>510</v>
-      </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>404</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9493,10 +9373,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9519,19 +9399,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="O58" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9556,13 +9436,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>515</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>516</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9580,7 +9460,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9592,19 +9472,19 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>519</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>521</v>
+        <v>404</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9621,10 +9501,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9647,16 +9527,18 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>161</v>
+        <v>518</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>162</v>
+        <v>519</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>163</v>
+        <v>520</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9704,7 +9586,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>164</v>
+        <v>517</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9716,7 +9598,7 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9728,7 +9610,7 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>165</v>
+        <v>522</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9752,14 +9634,14 @@
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -9771,17 +9653,15 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>141</v>
+        <v>524</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>525</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9830,19 +9710,19 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>171</v>
+        <v>523</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -9851,10 +9731,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>165</v>
+        <v>526</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9871,14 +9751,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9891,26 +9771,24 @@
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>140</v>
+        <v>528</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9958,7 +9836,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9970,7 +9848,7 @@
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -9979,10 +9857,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>84</v>
+        <v>532</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>137</v>
+        <v>533</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9999,10 +9877,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10013,7 +9891,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10022,18 +9900,20 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10082,16 +9962,16 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10103,10 +9983,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10123,10 +10003,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10137,7 +10017,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10146,19 +10026,23 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10206,16 +10090,16 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10227,10 +10111,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10247,10 +10131,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>540</v>
+        <v>547</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10273,20 +10157,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>541</v>
+        <v>162</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10310,13 +10190,13 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>545</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>546</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
@@ -10334,7 +10214,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>540</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10346,19 +10226,19 @@
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>443</v>
+        <v>165</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10375,14 +10255,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10401,20 +10281,18 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>550</v>
+        <v>141</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>551</v>
+        <v>167</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10438,13 +10316,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>554</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>555</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10462,7 +10340,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>549</v>
+        <v>171</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10474,19 +10352,19 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>443</v>
+        <v>165</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -10503,43 +10381,45 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>486</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>557</v>
+        <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>558</v>
+        <v>487</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>560</v>
+        <v>149</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10588,19 +10468,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>556</v>
+        <v>489</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10612,7 +10492,7 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>561</v>
+        <v>137</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -10629,10 +10509,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10640,7 +10520,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>94</v>
@@ -10652,19 +10532,23 @@
         <v>84</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>563</v>
+        <v>551</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>552</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10688,13 +10572,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>84</v>
+        <v>555</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10712,10 +10596,10 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>94</v>
@@ -10730,16 +10614,16 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>84</v>
+        <v>556</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>534</v>
+        <v>280</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>565</v>
+        <v>281</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>84</v>
@@ -10753,10 +10637,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10767,7 +10651,7 @@
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -10779,18 +10663,20 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>569</v>
+        <v>372</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10838,13 +10724,13 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
@@ -10856,19 +10742,19 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>84</v>
+        <v>561</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>571</v>
+        <v>377</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>572</v>
+        <v>378</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10879,10 +10765,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10893,7 +10779,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10902,21 +10788,23 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>574</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10940,13 +10828,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>390</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10964,16 +10852,16 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>84</v>
+        <v>392</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10985,10 +10873,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>571</v>
+        <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>578</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11005,14 +10893,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>84</v>
+        <v>395</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11028,22 +10916,22 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>514</v>
+        <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>580</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>581</v>
+        <v>397</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>582</v>
+        <v>398</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>583</v>
+        <v>399</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11068,13 +10956,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11092,7 +10980,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11110,19 +10998,19 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>584</v>
+        <v>403</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>585</v>
+        <v>404</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11133,10 +11021,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11147,7 +11035,7 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11159,16 +11047,20 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>162</v>
+        <v>568</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11216,19 +11108,19 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>164</v>
+        <v>567</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11237,10 +11129,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>165</v>
+        <v>482</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11252,905 +11144,11 @@
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR78" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR78">
+  <autoFilter ref="A1:AR71">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12160,7 +11158,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -662,13 +662,13 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1241: source value from V HEALTH FACTORS - IEN (#9000010.23-.001)</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
     <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>1241: source value from V HEALTH FACTORS - IEN (#9000010.23-.001)</t>
   </si>
   <si>
     <t>Observation.identifier.period</t>
@@ -797,6 +797,9 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-observation-smoking-status-status</t>
   </si>
   <si>
+    <t>1242: fixed value = #final</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -810,9 +813,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1242: fixed value = #final</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -848,13 +848,13 @@
 </t>
   </si>
   <si>
+    <t>1243: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#social-history</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>1243: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#social-history</t>
   </si>
   <si>
     <t>Observation.category:SocialHistory</t>
@@ -931,16 +931,16 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
+    <t>1244: transform using http://loinc.org#72166-2 on HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
+  </si>
+  <si>
+    <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
+  </si>
+  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>1244: transform using http://loinc.org#72166-2 on HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
-  </si>
-  <si>
-    <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -986,6 +986,9 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>1245: reference from V HEALTH FACTOR - PATIENT NAME (#9000010.23-.02)</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -996,9 +999,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>1245: reference from V HEALTH FACTOR - PATIENT NAME (#9000010.23-.02)</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1043,6 +1043,12 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
+    <t>1246: reference from V HEALTH FACTOR - VISIT (#9000010.23-.03)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.VisitDateTime</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1053,12 +1059,6 @@
   </si>
   <si>
     <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>1246: reference from V HEALTH FACTOR - VISIT (#9000010.23-.03)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.VisitDateTime</t>
   </si>
   <si>
     <t>Observation.effective[x]</t>
@@ -1156,6 +1156,9 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>1248: reference from V HEALTH FACTOR - ENCOUNTER PROVIDER (#9000010.23-1204)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1166,9 +1169,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>1248: reference from V HEALTH FACTOR - ENCOUNTER PROVIDER (#9000010.23-1204)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1367,13 +1367,13 @@
     <t>Annotation.text</t>
   </si>
   <si>
+    <t>1250: source value from V HEALTH FACTOR - COMMENTS (#9000010.23-81101)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.Comments</t>
+  </si>
+  <si>
     <t>Act.text</t>
-  </si>
-  <si>
-    <t>1250: source value from V HEALTH FACTOR - COMMENTS (#9000010.23-81101)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.Comments</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2151,14 +2151,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="109.28515625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="49.95703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.28515625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="49.95703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2397,22 +2397,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3034,13 +3034,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3160,13 +3160,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -3286,13 +3286,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3414,13 +3414,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3531,25 +3531,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3664,13 +3664,13 @@
         <v>84</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3790,13 +3790,13 @@
         <v>84</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3915,16 +3915,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -4043,16 +4043,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4171,16 +4171,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4291,25 +4291,25 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AO17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
         <v>84</v>
@@ -4421,16 +4421,16 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4547,16 +4547,16 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4667,22 +4667,22 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4793,22 +4793,22 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4922,19 +4922,19 @@
         <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
         <v>256</v>
@@ -5045,7 +5045,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>266</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5054,13 +5054,13 @@
         <v>84</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>268</v>
@@ -5184,16 +5184,16 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c r="AO24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AP24" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ24" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5301,28 +5301,28 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AO25" t="s" s="2">
+      <c r="AQ25" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AP25" t="s" s="2">
+      <c r="AR25" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AQ25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR25" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5434,13 +5434,13 @@
         <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ26" t="s" s="2">
         <v>84</v>
@@ -5560,13 +5560,13 @@
         <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5679,28 +5679,28 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>295</v>
+        <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>296</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5813,16 +5813,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5944,13 +5944,13 @@
         <v>312</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AO30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>315</v>
@@ -6067,19 +6067,19 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AO31" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6192,25 +6192,25 @@
         <v>329</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>84</v>
+        <v>330</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>331</v>
+        <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>332</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>84</v>
+        <v>333</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -6315,25 +6315,25 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AP33" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO33" t="s" s="2">
+      <c r="AQ33" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6445,28 +6445,28 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>350</v>
-      </c>
       <c r="AR34" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -6577,19 +6577,19 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AP35" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AO35" t="s" s="2">
+      <c r="AQ35" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6706,13 +6706,13 @@
         <v>366</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>369</v>
@@ -6826,25 +6826,25 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
+      <c r="AQ37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
@@ -6951,28 +6951,28 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>384</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR38" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -7085,16 +7085,16 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7210,25 +7210,25 @@
         <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
@@ -7341,16 +7341,16 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7468,13 +7468,13 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP42" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7594,13 +7594,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7717,16 +7717,16 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7841,16 +7841,16 @@
         <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7959,28 +7959,28 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AP46" t="s" s="2">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>435</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
@@ -8088,25 +8088,25 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -8219,16 +8219,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8342,25 +8342,25 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8468,25 +8468,25 @@
         <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -8599,16 +8599,16 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8726,13 +8726,13 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8852,13 +8852,13 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -8980,13 +8980,13 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP54" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9101,16 +9101,16 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AP55" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9225,16 +9225,16 @@
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AP56" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9350,19 +9350,19 @@
         <v>84</v>
       </c>
       <c r="AL57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AP57" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9478,19 +9478,19 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AP58" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9610,13 +9610,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9731,16 +9731,16 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AP60" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9857,16 +9857,16 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AP61" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9983,16 +9983,16 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AP62" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10111,16 +10111,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AP63" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10238,13 +10238,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10364,13 +10364,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10492,13 +10492,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10614,22 +10614,22 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN67" t="s" s="2">
+      <c r="AP67" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AO67" t="s" s="2">
+      <c r="AQ67" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10742,25 +10742,25 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AP68" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
+      <c r="AQ68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR68" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR68" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
@@ -10873,16 +10873,16 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN69" t="s" s="2">
+      <c r="AP69" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10998,25 +10998,25 @@
         <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
@@ -11129,16 +11129,16 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AN71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -828,6 +828,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:SocialHistory</t>
+  </si>
+  <si>
+    <t>SocialHistory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -838,29 +860,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>1243: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#social-history</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:SocialHistory</t>
-  </si>
-  <si>
-    <t>SocialHistory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -931,7 +931,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1244: transform using http://loinc.org#72166-2 on HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
+    <t>1244: fixed value = http://loinc.org#72166-2 when HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
   </si>
   <si>
     <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
@@ -2151,7 +2151,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="109.28515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="109.640625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="49.95703125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
@@ -4993,7 +4993,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5011,16 +5011,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5045,25 +5045,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5071,13 +5071,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>257</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5121,7 +5121,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5139,10 +5139,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5175,7 +5175,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>84</v>
+        <v>270</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
@@ -5190,10 +5190,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V HEALTH FACTORS (#9000010.23) to us-core-smokingstatus</t>
+    <t>This StructureDefinition contains the maps for VistA file V HEALTH FACTORS (9000010.23) to us-core-smokingstatus</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -662,7 +662,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1241: source value from V HEALTH FACTORS - IEN (#9000010.23-.001)</t>
+    <t>1241: source value from V HEALTH FACTORS - IEN (9000010.23-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -931,7 +931,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1244: fixed value = http://loinc.org#72166-2 when HEALTH FACTORS - CATEGORY (#9999999.64-.03) case TOBACCO</t>
+    <t>1244: fixed value = http://loinc.org#72166-2 when HEALTH FACTORS - CATEGORY (9999999.64-.03) case TOBACCO</t>
   </si>
   <si>
     <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
@@ -986,7 +986,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1245: reference from V HEALTH FACTOR - PATIENT NAME (#9000010.23-.02)</t>
+    <t>1245: reference from V HEALTH FACTOR - PATIENT NAME (9000010.23-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1043,7 +1043,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>1246: reference from V HEALTH FACTOR - VISIT (#9000010.23-.03)</t>
+    <t>1246: reference from V HEALTH FACTOR - VISIT (9000010.23-.03)</t>
   </si>
   <si>
     <t>HF.HealthFactor.VisitDateTime</t>
@@ -1109,7 +1109,7 @@
     <t>effectiveDateTime</t>
   </si>
   <si>
-    <t>1247: source value from V HEALTH FACTOR - EVENT DATE AND TIME (#9000010.23-1201)</t>
+    <t>1247: source value from V HEALTH FACTOR - EVENT DATE AND TIME (9000010.23-1201)</t>
   </si>
   <si>
     <t>HF.HealthFactor.EventDateTime</t>
@@ -1156,7 +1156,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1248: reference from V HEALTH FACTOR - ENCOUNTER PROVIDER (#9000010.23-1204)</t>
+    <t>1248: reference from V HEALTH FACTOR - ENCOUNTER PROVIDER (9000010.23-1204)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1214,7 +1214,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFSmokingStatus</t>
   </si>
   <si>
-    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTOR - HEALTH FACTOR (#9000010.23-.01)</t>
+    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTOR - HEALTH FACTOR (9000010.23-.01)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1367,7 +1367,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1250: source value from V HEALTH FACTOR - COMMENTS (#9000010.23-81101)</t>
+    <t>1250: source value from V HEALTH FACTOR - COMMENTS (9000010.23-81101)</t>
   </si>
   <si>
     <t>HF.HealthFactor.Comments</t>
@@ -2151,7 +2151,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="109.640625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="108.10546875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="49.95703125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -986,7 +986,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1245: reference from V HEALTH FACTOR - PATIENT NAME (9000010.23-.02)</t>
+    <t>1245: reference from V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1043,7 +1043,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>1246: reference from V HEALTH FACTOR - VISIT (9000010.23-.03)</t>
+    <t>1246: reference from V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
   </si>
   <si>
     <t>HF.HealthFactor.VisitDateTime</t>
@@ -1109,7 +1109,7 @@
     <t>effectiveDateTime</t>
   </si>
   <si>
-    <t>1247: source value from V HEALTH FACTOR - EVENT DATE AND TIME (9000010.23-1201)</t>
+    <t>1247: source value from V HEALTH FACTORS - EVENT DATE AND TIME (9000010.23-1201)</t>
   </si>
   <si>
     <t>HF.HealthFactor.EventDateTime</t>
@@ -1156,7 +1156,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1248: reference from V HEALTH FACTOR - ENCOUNTER PROVIDER (9000010.23-1204)</t>
+    <t>1248: reference from V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1214,7 +1214,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFSmokingStatus</t>
   </si>
   <si>
-    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTOR - HEALTH FACTOR (9000010.23-.01)</t>
+    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTORS - HEALTH FACTOR (9000010.23-.01)</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1367,7 +1367,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1250: source value from V HEALTH FACTOR - COMMENTS (9000010.23-81101)</t>
+    <t>1250: source value from V HEALTH FACTORS - COMMENTS (9000010.23-81101)</t>
   </si>
   <si>
     <t>HF.HealthFactor.Comments</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="573">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -989,6 +989,9 @@
     <t>1245: reference from V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
   </si>
   <si>
+    <t>HF.HealthFactor.PatientIEN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -1046,7 +1049,7 @@
     <t>1246: reference from V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
   </si>
   <si>
-    <t>HF.HealthFactor.VisitDateTime</t>
+    <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1159,6 +1162,9 @@
     <t>1248: reference from V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
   </si>
   <si>
+    <t>HF.HealthFactor.EncounterStaffIEN</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1215,6 +1221,9 @@
   </si>
   <si>
     <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTORS - HEALTH FACTOR (9000010.23-.01)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2152,7 +2161,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="108.10546875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="49.95703125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="52.3125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -5938,22 +5947,22 @@
         <v>311</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5961,10 +5970,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5987,16 +5996,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6046,7 +6055,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6076,10 +6085,10 @@
         <v>280</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6087,14 +6096,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6113,19 +6122,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6174,7 +6183,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6189,25 +6198,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6215,14 +6224,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6241,19 +6250,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6290,17 +6299,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6321,19 +6330,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6341,16 +6350,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6369,19 +6378,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6430,7 +6439,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6445,25 +6454,25 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6471,10 +6480,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6497,16 +6506,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6556,7 +6565,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6583,13 +6592,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6597,10 +6606,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6623,17 +6632,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6682,7 +6691,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6697,25 +6706,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6723,10 +6732,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6752,16 +6761,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6798,17 +6807,17 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6817,7 +6826,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6832,30 +6841,30 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
@@ -6880,16 +6889,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6918,7 +6927,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6936,7 +6945,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6945,42 +6954,42 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7006,16 +7015,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7043,10 +7052,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7064,7 +7073,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7073,7 +7082,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7094,7 +7103,7 @@
         <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7105,14 +7114,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7134,16 +7143,16 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7171,10 +7180,10 @@
         <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7192,7 +7201,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7216,27 +7225,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7259,19 +7268,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7320,7 +7329,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7347,10 +7356,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7361,10 +7370,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7485,10 +7494,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7611,10 +7620,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7637,16 +7646,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7696,7 +7705,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7726,7 +7735,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7737,10 +7746,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7763,13 +7772,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7820,7 +7829,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7850,7 +7859,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7861,10 +7870,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7887,13 +7896,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7944,7 +7953,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -7959,10 +7968,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -7974,7 +7983,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7985,10 +7994,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8014,13 +8023,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8046,13 +8055,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8070,7 +8079,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8094,27 +8103,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8140,16 +8149,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8174,13 +8183,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8198,7 +8207,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8225,10 +8234,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8239,10 +8248,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8265,16 +8274,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8324,7 +8333,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8348,27 +8357,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8391,16 +8400,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8450,7 +8459,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8474,27 +8483,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8517,19 +8526,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8578,7 +8587,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8590,7 +8599,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8605,10 +8614,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8619,10 +8628,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8743,10 +8752,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8869,14 +8878,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8898,10 +8907,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8956,7 +8965,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -8997,10 +9006,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9023,13 +9032,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9080,7 +9089,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9089,7 +9098,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9107,10 +9116,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9121,10 +9130,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9147,13 +9156,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9204,7 +9213,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9213,7 +9222,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9231,10 +9240,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9245,10 +9254,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9274,16 +9283,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9311,10 +9320,10 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9332,7 +9341,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9356,13 +9365,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9373,10 +9382,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9402,16 +9411,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9436,13 +9445,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9460,7 +9469,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9484,13 +9493,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9501,10 +9510,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9527,17 +9536,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9586,7 +9595,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9616,7 +9625,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9627,10 +9636,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9656,10 +9665,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9710,7 +9719,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9737,10 +9746,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9751,10 +9760,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9777,16 +9786,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9836,7 +9845,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9863,10 +9872,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9877,10 +9886,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9903,16 +9912,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9962,7 +9971,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9989,10 +9998,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10003,10 +10012,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10029,19 +10038,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10090,7 +10099,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10117,10 +10126,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10131,10 +10140,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10255,10 +10264,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10381,14 +10390,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10410,10 +10419,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10468,7 +10477,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10509,10 +10518,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10538,13 +10547,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>276</v>
@@ -10572,13 +10581,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10596,7 +10605,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10620,7 +10629,7 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>280</v>
@@ -10637,10 +10646,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10663,19 +10672,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10724,7 +10733,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10748,27 +10757,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10794,16 +10803,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10831,10 +10840,10 @@
         <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10852,7 +10861,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10861,7 +10870,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10882,7 +10891,7 @@
         <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10893,14 +10902,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10922,16 +10931,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10959,10 +10968,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -10980,7 +10989,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11004,27 +11013,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11050,16 +11059,16 @@
         <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11108,7 +11117,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11135,10 +11144,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3058" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,10 +632,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1241-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -1224,6 +1230,36 @@
   </si>
   <si>
     <t>HF.HealthFactor.HealthFactorTypeIEN</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.value[x].text</t>
+  </si>
+  <si>
+    <t>[HEALTH FACTOR]</t>
+  </si>
+  <si>
+    <t>1249-1: fixed value = [HEALTH FACTOR]</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2122,10 +2158,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR71"/>
+  <dimension ref="A1:AR75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4089,7 +4125,7 @@
         <v>94</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>84</v>
@@ -4120,10 +4156,10 @@
         <v>84</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>84</v>
@@ -4159,7 +4195,7 @@
         <v>84</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4174,7 +4210,7 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>84</v>
@@ -4186,10 +4222,10 @@
         <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -4200,10 +4236,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4229,13 +4265,13 @@
         <v>161</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4249,7 +4285,7 @@
         <v>84</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>84</v>
@@ -4285,7 +4321,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -4300,7 +4336,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -4312,10 +4348,10 @@
         <v>84</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
@@ -4326,10 +4362,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4352,13 +4388,13 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4409,7 +4445,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -4436,10 +4472,10 @@
         <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
@@ -4450,10 +4486,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4476,16 +4512,16 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4535,7 +4571,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -4562,10 +4598,10 @@
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
@@ -4576,14 +4612,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4602,17 +4638,17 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -4661,7 +4697,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -4682,16 +4718,16 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
@@ -4702,14 +4738,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4728,16 +4764,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4787,7 +4823,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -4808,16 +4844,16 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
@@ -4828,10 +4864,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4857,16 +4893,16 @@
         <v>114</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>84</v>
@@ -4876,7 +4912,7 @@
         <v>84</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>84</v>
@@ -4895,7 +4931,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>84</v>
@@ -4913,7 +4949,7 @@
         <v>84</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>94</v>
@@ -4928,25 +4964,25 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4954,10 +4990,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4983,16 +5019,16 @@
         <v>183</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>84</v>
@@ -5020,16 +5056,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5039,7 +5075,7 @@
         <v>170</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>82</v>
@@ -5069,10 +5105,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5080,13 +5116,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5111,16 +5147,16 @@
         <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
@@ -5130,7 +5166,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5148,10 +5184,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5169,7 +5205,7 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5184,7 +5220,7 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>84</v>
@@ -5199,10 +5235,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5210,14 +5246,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5239,16 +5275,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5277,7 +5313,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5295,7 +5331,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5316,30 +5352,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5460,10 +5496,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5586,10 +5622,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5612,19 +5648,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5673,7 +5709,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5688,10 +5724,10 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>84</v>
@@ -5700,10 +5736,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5714,10 +5750,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5743,16 +5779,16 @@
         <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5801,7 +5837,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5828,10 +5864,10 @@
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5842,10 +5878,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5868,19 +5904,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5929,7 +5965,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5944,25 +5980,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5970,10 +6006,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5996,16 +6032,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6055,7 +6091,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6082,13 +6118,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6096,14 +6132,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6122,19 +6158,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6183,7 +6219,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6198,25 +6234,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6224,14 +6260,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6250,19 +6286,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6299,17 +6335,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6330,19 +6366,19 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>84</v>
@@ -6350,16 +6386,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6378,19 +6414,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6439,7 +6475,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6454,25 +6490,25 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>84</v>
@@ -6480,10 +6516,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6506,16 +6542,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6565,7 +6601,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6592,13 +6628,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6606,10 +6642,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6632,17 +6668,17 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6691,7 +6727,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6706,25 +6742,25 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6732,10 +6768,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6761,16 +6797,16 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6807,17 +6843,17 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6826,7 +6862,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6841,30 +6877,30 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
@@ -6889,16 +6925,16 @@
         <v>183</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6927,7 +6963,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6945,7 +6981,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6954,42 +6990,42 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7012,20 +7048,16 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>389</v>
+        <v>162</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7049,13 +7081,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>394</v>
+        <v>84</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7073,7 +7105,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>388</v>
+        <v>164</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7082,10 +7114,10 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7100,10 +7132,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>396</v>
+        <v>165</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7114,14 +7146,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>398</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7140,20 +7172,18 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>167</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>402</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7177,31 +7207,31 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>171</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7213,7 +7243,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7225,27 +7255,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>407</v>
+        <v>165</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7265,22 +7295,22 @@
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>410</v>
+        <v>289</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>411</v>
+        <v>290</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>412</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>414</v>
+        <v>293</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7329,7 +7359,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>409</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7356,10 +7386,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>415</v>
+        <v>297</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>416</v>
+        <v>298</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7370,10 +7400,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7387,25 +7417,29 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>162</v>
+        <v>300</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7414,7 +7448,7 @@
         <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>84</v>
@@ -7453,7 +7487,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7465,10 +7499,10 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>84</v>
@@ -7480,10 +7514,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7494,21 +7528,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7520,18 +7554,20 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>141</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>167</v>
+        <v>402</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7555,43 +7591,43 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>84</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>84</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>171</v>
+        <v>400</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7606,10 +7642,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>165</v>
+        <v>408</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7620,21 +7656,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>84</v>
+        <v>410</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7643,21 +7679,23 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>420</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7681,13 +7719,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>84</v>
+        <v>415</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7705,13 +7743,13 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
@@ -7729,27 +7767,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>84</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>137</v>
+        <v>418</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7760,7 +7798,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7769,19 +7807,23 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>338</v>
+        <v>422</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7829,13 +7871,13 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
@@ -7856,10 +7898,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>137</v>
+        <v>427</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7870,10 +7912,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7881,28 +7923,28 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>432</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>433</v>
+        <v>162</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>434</v>
+        <v>163</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7953,10 +7995,10 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>94</v>
@@ -7965,13 +8007,13 @@
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>436</v>
+        <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -7980,10 +8022,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>438</v>
+        <v>165</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7994,21 +8036,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8020,16 +8062,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>141</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>167</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>442</v>
+        <v>143</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8055,43 +8097,43 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>445</v>
+        <v>84</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>171</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8103,27 +8145,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>447</v>
+        <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>448</v>
+        <v>165</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8143,23 +8185,21 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>432</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>454</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8183,13 +8223,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8207,7 +8247,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8234,10 +8274,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8248,10 +8288,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8271,20 +8311,18 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>460</v>
+        <v>340</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8333,7 +8371,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8357,27 +8395,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>465</v>
+        <v>137</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>468</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8385,32 +8423,30 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>472</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8459,10 +8495,10 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>94</v>
@@ -8474,36 +8510,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>473</v>
+        <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>474</v>
+        <v>137</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>475</v>
+        <v>450</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8514,7 +8550,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8526,20 +8562,18 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>478</v>
+        <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8563,13 +8597,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8587,19 +8621,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>483</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8611,27 +8645,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8654,16 +8688,20 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>162</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8687,13 +8725,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>84</v>
+        <v>467</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8711,7 +8749,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>164</v>
+        <v>462</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8723,7 +8761,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8738,10 +8776,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>165</v>
+        <v>470</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8752,21 +8790,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8778,16 +8816,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>140</v>
+        <v>472</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>141</v>
+        <v>473</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>167</v>
+        <v>474</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>143</v>
+        <v>475</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8837,19 +8875,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>171</v>
+        <v>471</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8861,63 +8899,61 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>84</v>
+        <v>476</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>165</v>
+        <v>478</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>84</v>
+        <v>479</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>481</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -8965,19 +9001,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -8989,27 +9025,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>84</v>
+        <v>485</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>84</v>
+        <v>486</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>137</v>
+        <v>487</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9020,7 +9056,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9032,16 +9068,20 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O55" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9089,37 +9129,37 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9130,10 +9170,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9156,13 +9196,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>494</v>
+        <v>161</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>501</v>
+        <v>162</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>502</v>
+        <v>163</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9213,7 +9253,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>500</v>
+        <v>164</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9222,10 +9262,10 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>497</v>
+        <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9240,10 +9280,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>498</v>
+        <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>503</v>
+        <v>165</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9254,21 +9294,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9280,20 +9320,18 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>505</v>
+        <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>506</v>
+        <v>167</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9317,13 +9355,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9341,19 +9379,19 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>504</v>
+        <v>171</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9365,13 +9403,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>511</v>
+        <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>407</v>
+        <v>165</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9382,14 +9420,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>84</v>
+        <v>501</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9402,25 +9440,25 @@
         <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>516</v>
+        <v>143</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>517</v>
+        <v>149</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9445,13 +9483,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>518</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9469,7 +9507,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9481,7 +9519,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9493,13 +9531,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>511</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>407</v>
+        <v>137</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9510,10 +9548,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9536,18 +9574,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" t="s" s="2">
-        <v>524</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9595,7 +9631,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9604,7 +9640,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>84</v>
+        <v>509</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9622,10 +9658,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>510</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9636,10 +9672,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9662,13 +9698,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>161</v>
+        <v>506</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>527</v>
+        <v>513</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9719,7 +9755,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>526</v>
+        <v>512</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9728,7 +9764,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>84</v>
+        <v>509</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9746,10 +9782,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9760,10 +9796,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9774,7 +9810,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -9783,21 +9819,23 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>531</v>
+        <v>183</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9821,13 +9859,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9845,13 +9883,13 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
@@ -9869,13 +9907,13 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>84</v>
+        <v>523</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>536</v>
+        <v>419</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9886,10 +9924,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9909,21 +9947,23 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>538</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9947,13 +9987,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>84</v>
+        <v>530</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>84</v>
+        <v>531</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -9971,7 +10011,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -9995,13 +10035,13 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>84</v>
+        <v>523</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>542</v>
+        <v>419</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10012,10 +10052,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10026,7 +10066,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10035,22 +10075,20 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10099,13 +10137,13 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>84</v>
@@ -10126,10 +10164,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>548</v>
+        <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10140,10 +10178,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10169,10 +10207,10 @@
         <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>162</v>
+        <v>539</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>163</v>
+        <v>540</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10223,7 +10261,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>164</v>
+        <v>538</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10235,7 +10273,7 @@
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10250,10 +10288,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>84</v>
+        <v>510</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>165</v>
+        <v>541</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10264,14 +10302,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10287,19 +10325,19 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>140</v>
+        <v>543</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>141</v>
+        <v>544</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>167</v>
+        <v>545</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>143</v>
+        <v>546</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10349,7 +10387,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>171</v>
+        <v>542</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10361,7 +10399,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10376,10 +10414,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>165</v>
+        <v>548</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10390,14 +10428,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>489</v>
+        <v>84</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10410,26 +10448,24 @@
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>140</v>
+        <v>550</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>551</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>491</v>
+        <v>552</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10477,7 +10513,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>549</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10489,7 +10525,7 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10504,10 +10540,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>84</v>
+        <v>547</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>137</v>
+        <v>554</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10518,10 +10554,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10529,10 +10565,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10544,19 +10580,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>183</v>
+        <v>490</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>276</v>
+        <v>559</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10581,13 +10617,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>557</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>558</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10605,13 +10641,13 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
@@ -10629,16 +10665,16 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>280</v>
+        <v>560</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>281</v>
+        <v>561</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>282</v>
+        <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10646,10 +10682,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10669,23 +10705,19 @@
         <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>561</v>
+        <v>161</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>562</v>
+        <v>162</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10733,7 +10765,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>560</v>
+        <v>164</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10745,7 +10777,7 @@
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10757,38 +10789,38 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>564</v>
+        <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>380</v>
+        <v>165</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>381</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10800,20 +10832,18 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>566</v>
+        <v>141</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>567</v>
+        <v>167</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10837,13 +10867,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>393</v>
+        <v>84</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>394</v>
+        <v>84</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10861,19 +10891,19 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>565</v>
+        <v>171</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>395</v>
+        <v>84</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>84</v>
@@ -10888,10 +10918,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>396</v>
+        <v>165</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10902,14 +10932,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>398</v>
+        <v>501</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10922,25 +10952,25 @@
         <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>399</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>400</v>
+        <v>503</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>401</v>
+        <v>143</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>402</v>
+        <v>149</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10965,13 +10995,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>403</v>
+        <v>84</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>404</v>
+        <v>84</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -10989,7 +11019,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>569</v>
+        <v>504</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11001,7 +11031,7 @@
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>84</v>
@@ -11013,27 +11043,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>407</v>
+        <v>137</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>408</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11041,10 +11071,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11053,22 +11083,22 @@
         <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>481</v>
+        <v>568</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>482</v>
+        <v>278</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11093,13 +11123,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11117,13 +11147,13 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
@@ -11141,23 +11171,535 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>84</v>
+        <v>571</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>484</v>
+        <v>282</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>485</v>
+        <v>283</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AR71" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR75" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR71">
+  <autoFilter ref="A1:AR75">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11167,7 +11709,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI70">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/9000010.23</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1241-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1241-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/9000010.23</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -632,7 +632,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/9000010.23</t>
+    <t>http://va.gov/identifiers/$Sta3n/9000010.23</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -641,7 +641,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1241-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/9000010.23</t>
+    <t>1241-1: fixed value = http://va.gov/identifiers/$Sta3n/9000010.23</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -937,10 +937,11 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1244: fixed value = http://loinc.org#72166-2 when HEALTH FACTORS - CATEGORY (9999999.64-.03) case TOBACCO</t>
-  </si>
-  <si>
-    <t>Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
+    <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN
+Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -2196,7 +2197,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="108.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="166.92578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="52.3125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$71</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3058" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -891,6 +891,13 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes</t>
   </si>
   <si>
+    <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN
+Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -909,13 +916,282 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
+    <t>Observation.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+</t>
+  </si>
+  <si>
+    <t>Who and/or what the observation is about</t>
+  </si>
+  <si>
+    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+  </si>
+  <si>
+    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
+  </si>
+  <si>
+    <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>1245: reference from V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.PatientIEN</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>PID-3</t>
+  </si>
+  <si>
+    <t>participation[typeCode=RTGT]</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>Observation.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>What the observation is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
+  </si>
+  <si>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
+  </si>
+  <si>
+    <t>Observation.encounter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Context
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Encounter)
+</t>
+  </si>
+  <si>
+    <t>Healthcare event during which this observation is made</t>
+  </si>
+  <si>
+    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
+  </si>
+  <si>
+    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
+  </si>
+  <si>
+    <t>1246: reference from V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
+  </si>
+  <si>
+    <t>Event.context</t>
+  </si>
+  <si>
+    <t>PV1</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
+  </si>
+  <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occurrence
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Clinically relevant time/time-period for observation</t>
+  </si>
+  <si>
+    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+  </si>
+  <si>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+  </si>
+  <si>
+    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.done[x]</t>
+  </si>
+  <si>
+    <t>Observation.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t>1247: source value from V HEALTH FACTORS - EVENT DATE AND TIME (9000010.23-1201)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.EventDateTime</t>
+  </si>
+  <si>
+    <t>Observation.issued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Date/Time this version was made available</t>
+  </si>
+  <si>
+    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
+  </si>
+  <si>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+  </si>
+  <si>
+    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
+  </si>
+  <si>
+    <t>participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>Observation.performer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>Who is responsible for the observation</t>
+  </si>
+  <si>
+    <t>Who was responsible for asserting the observed value as "true".</t>
+  </si>
+  <si>
+    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
+  </si>
+  <si>
+    <t>1248: reference from V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.EncounterStaffIEN</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
+    <t>&lt; 441742003 |Evaluation finding|</t>
+  </si>
+  <si>
+    <t>OBX.2, OBX.5, OBX.6</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Coded Responses from Smoking Status Value Set</t>
+  </si>
+  <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFSmokingStatus</t>
+  </si>
+  <si>
+    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN
+Dim.HealthFactorType.HealthFactorCategory,Dim.HealthFactorType.HealthFactorType</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.id</t>
+  </si>
+  <si>
+    <t>Observation.value[x].id</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x].extension</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>Observation.value[x].coding</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -937,20 +1213,16 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.HealthFactorTypeIEN
-Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
-  </si>
-  <si>
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.code.text</t>
+    <t>Observation.value[x]:valueCodeableConcept.text</t>
+  </si>
+  <si>
+    <t>Observation.value[x].text</t>
   </si>
   <si>
     <t>Plain text representation of the concept</t>
@@ -965,302 +1237,19 @@
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
+    <t>[HEALTH FACTOR]</t>
+  </si>
+  <si>
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1249-1: fixed value = [HEALTH FACTOR]</t>
+  </si>
+  <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Observation.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
-</t>
-  </si>
-  <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
-  </si>
-  <si>
-    <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
-  </si>
-  <si>
-    <t>Observations have no value if you don't know who or what they're about.</t>
-  </si>
-  <si>
-    <t>1245: reference from V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.PatientIEN</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>PID-3</t>
-  </si>
-  <si>
-    <t>participation[typeCode=RTGT]</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>Observation.focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Resource)
-</t>
-  </si>
-  <si>
-    <t>What the observation is about, when it is not about the subject of record</t>
-  </si>
-  <si>
-    <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
-  </si>
-  <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>participation[typeCode=SBJ]</t>
-  </si>
-  <si>
-    <t>Observation.encounter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Context
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Encounter)
-</t>
-  </si>
-  <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
-  </si>
-  <si>
-    <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
-  </si>
-  <si>
-    <t>1246: reference from V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
-  </si>
-  <si>
-    <t>Event.context</t>
-  </si>
-  <si>
-    <t>PV1</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=ENC, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occurrence
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
-  </si>
-  <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
-  </si>
-  <si>
-    <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>OBX-14, and/or OBX-19 after v2.4  (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.done[x]</t>
-  </si>
-  <si>
-    <t>Observation.effective[x]:effectiveDateTime</t>
-  </si>
-  <si>
-    <t>effectiveDateTime</t>
-  </si>
-  <si>
-    <t>1247: source value from V HEALTH FACTORS - EVENT DATE AND TIME (9000010.23-1201)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.EventDateTime</t>
-  </si>
-  <si>
-    <t>Observation.issued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Date/Time this version was made available</t>
-  </si>
-  <si>
-    <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
-  </si>
-  <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
-  </si>
-  <si>
-    <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
-  </si>
-  <si>
-    <t>participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>Observation.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
-</t>
-  </si>
-  <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
-  </si>
-  <si>
-    <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
-  </si>
-  <si>
-    <t>1248: reference from V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.EncounterStaffIEN</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.value[x]</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>&lt; 441742003 |Evaluation finding|</t>
-  </si>
-  <si>
-    <t>OBX.2, OBX.5, OBX.6</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Coded Responses from Smoking Status Value Set</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFSmokingStatus</t>
-  </si>
-  <si>
-    <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTORS - HEALTH FACTOR (9000010.23-.01)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>[HEALTH FACTOR]</t>
-  </si>
-  <si>
-    <t>1249-1: fixed value = [HEALTH FACTOR]</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2159,7 +2148,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR75"/>
+  <dimension ref="A1:AR71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.69140625" customWidth="true" bestFit="true"/>
@@ -2198,7 +2187,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="166.92578125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="52.3125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="80.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -5347,36 +5336,36 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5384,31 +5373,35 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>161</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>162</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5456,7 +5449,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>164</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5468,28 +5461,28 @@
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>295</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>165</v>
+        <v>298</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5497,14 +5490,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5520,19 +5513,19 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>140</v>
+        <v>301</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>141</v>
+        <v>302</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>167</v>
+        <v>303</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>143</v>
+        <v>304</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5570,19 +5563,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5594,7 +5587,7 @@
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5609,13 +5602,13 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>165</v>
+        <v>305</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5623,21 +5616,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>95</v>
@@ -5649,19 +5642,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5710,13 +5703,13 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
@@ -5725,25 +5718,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5751,18 +5744,18 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>94</v>
@@ -5777,19 +5770,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>161</v>
+        <v>321</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5826,19 +5819,17 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>327</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5859,19 +5850,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5879,14 +5870,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5905,19 +5898,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5966,7 +5959,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5981,25 +5974,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -6007,10 +6000,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6021,7 +6014,7 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>84</v>
@@ -6033,16 +6026,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6092,13 +6085,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6119,13 +6112,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>282</v>
+        <v>341</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6133,21 +6126,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>95</v>
@@ -6159,19 +6152,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6220,13 +6211,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6235,25 +6226,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6261,14 +6252,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6287,19 +6278,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6336,17 +6327,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6355,7 +6346,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -6367,36 +6358,36 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
+        <v>364</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6415,19 +6406,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>340</v>
+        <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6452,13 +6443,11 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6476,7 +6465,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6485,42 +6474,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>347</v>
+        <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>84</v>
+        <v>361</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>350</v>
+        <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>364</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6540,20 +6529,18 @@
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>356</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>357</v>
+        <v>162</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6602,7 +6589,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>164</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6614,7 +6601,7 @@
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -6629,13 +6616,13 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>361</v>
+        <v>165</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>362</v>
+        <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>84</v>
@@ -6643,14 +6630,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6660,27 +6647,27 @@
         <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>364</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>365</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6716,19 +6703,19 @@
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>363</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6740,28 +6727,28 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>368</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>369</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>371</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>372</v>
+        <v>165</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6769,10 +6756,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6780,10 +6767,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>84</v>
@@ -6795,19 +6782,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>183</v>
+        <v>377</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6844,26 +6831,28 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>346</v>
+        <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6878,37 +6867,35 @@
         <v>84</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>94</v>
@@ -6923,19 +6910,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6945,7 +6932,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -6960,11 +6947,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6982,7 +6971,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6991,42 +6980,42 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>389</v>
+        <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>383</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7049,16 +7038,20 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>162</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7082,13 +7075,13 @@
         <v>84</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7106,7 +7099,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>164</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7115,10 +7108,10 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7133,10 +7126,10 @@
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>165</v>
+        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7147,14 +7140,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>139</v>
+        <v>406</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7173,18 +7166,20 @@
         <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>141</v>
+        <v>407</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>167</v>
+        <v>408</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7208,31 +7203,31 @@
         <v>84</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7244,7 +7239,7 @@
         <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7256,27 +7251,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>165</v>
+        <v>415</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7296,22 +7291,22 @@
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>289</v>
+        <v>418</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7360,7 +7355,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>294</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7387,10 +7382,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>297</v>
+        <v>423</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>298</v>
+        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7401,10 +7396,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7418,29 +7413,25 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>162</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7449,7 +7440,7 @@
         <v>84</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>84</v>
@@ -7488,7 +7479,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7500,10 +7491,10 @@
         <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>399</v>
+        <v>84</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>84</v>
@@ -7515,10 +7506,10 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>306</v>
+        <v>165</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7529,21 +7520,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>84</v>
@@ -7555,20 +7546,18 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>167</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>84</v>
       </c>
@@ -7592,43 +7581,43 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>406</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>400</v>
+        <v>171</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>84</v>
@@ -7643,10 +7632,10 @@
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>408</v>
+        <v>165</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7657,21 +7646,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>84</v>
@@ -7680,23 +7669,21 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>183</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7720,13 +7707,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>416</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -7744,13 +7731,13 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>84</v>
@@ -7768,27 +7755,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>417</v>
+        <v>84</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>418</v>
+        <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7799,7 +7786,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>84</v>
@@ -7808,23 +7795,19 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>422</v>
+        <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7872,13 +7855,13 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
@@ -7899,10 +7882,10 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>427</v>
+        <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7913,10 +7896,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7924,28 +7907,28 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
+        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7996,10 +7979,10 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>94</v>
@@ -8008,13 +7991,13 @@
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8023,10 +8006,10 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>165</v>
+        <v>446</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8037,21 +8020,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>84</v>
@@ -8063,16 +8046,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8098,43 +8081,43 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>84</v>
+        <v>452</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
@@ -8146,27 +8129,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>165</v>
+        <v>456</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8186,21 +8169,23 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>462</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8224,13 +8209,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8248,7 +8233,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8275,10 +8260,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>137</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>437</v>
+        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8289,10 +8274,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8312,18 +8297,20 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>340</v>
+        <v>468</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8372,7 +8359,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8396,27 +8383,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>137</v>
+        <v>473</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8424,30 +8411,32 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8496,10 +8485,10 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>447</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
         <v>94</v>
@@ -8511,36 +8500,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>137</v>
+        <v>482</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>450</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8551,7 +8540,7 @@
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -8563,18 +8552,20 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>486</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>452</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>453</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8598,13 +8589,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8622,19 +8613,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>491</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8646,27 +8637,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>458</v>
+        <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>459</v>
+        <v>492</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>460</v>
+        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>461</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8689,20 +8680,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>463</v>
+        <v>162</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8726,13 +8713,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8750,7 +8737,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>462</v>
+        <v>164</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8762,7 +8749,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8777,10 +8764,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>469</v>
+        <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>470</v>
+        <v>165</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8791,21 +8778,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>84</v>
@@ -8817,16 +8804,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>472</v>
+        <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>141</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
+        <v>167</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>475</v>
+        <v>143</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8876,19 +8863,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>171</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8900,61 +8887,63 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>477</v>
+        <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>478</v>
+        <v>165</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>479</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>481</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>482</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9002,19 +8991,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9026,27 +9015,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>487</v>
+        <v>137</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9057,7 +9046,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9069,20 +9058,16 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9130,19 +9115,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>84</v>
+        <v>505</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>495</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9157,10 +9142,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>496</v>
+        <v>506</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9171,10 +9156,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9197,13 +9182,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>161</v>
+        <v>502</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9254,7 +9239,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>164</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9263,10 +9248,10 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>505</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
@@ -9281,10 +9266,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>84</v>
+        <v>506</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>165</v>
+        <v>511</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9295,21 +9280,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>499</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9321,18 +9306,20 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>141</v>
+        <v>513</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>167</v>
+        <v>514</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9356,13 +9343,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>84</v>
+        <v>517</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>84</v>
+        <v>518</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9380,19 +9367,19 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>171</v>
+        <v>512</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>84</v>
@@ -9404,13 +9391,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>165</v>
+        <v>415</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9421,14 +9408,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>501</v>
+        <v>84</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9441,25 +9428,25 @@
         <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>143</v>
+        <v>524</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>149</v>
+        <v>525</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9484,13 +9471,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>527</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9508,7 +9495,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9520,7 +9507,7 @@
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9532,13 +9519,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>137</v>
+        <v>415</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9549,10 +9536,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9575,16 +9562,18 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>506</v>
+        <v>529</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>507</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9632,7 +9621,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>505</v>
+        <v>528</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9641,7 +9630,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9659,10 +9648,10 @@
         <v>84</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>511</v>
+        <v>533</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9673,10 +9662,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9699,13 +9688,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>506</v>
+        <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>513</v>
+        <v>535</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>514</v>
+        <v>536</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9756,7 +9745,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>512</v>
+        <v>534</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9765,7 +9754,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>509</v>
+        <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9783,10 +9772,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>515</v>
+        <v>537</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9797,10 +9786,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9811,7 +9800,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -9820,23 +9809,21 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>183</v>
+        <v>539</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>517</v>
+        <v>540</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>518</v>
+        <v>541</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -9860,13 +9847,13 @@
         <v>84</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>84</v>
@@ -9884,13 +9871,13 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>516</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
@@ -9908,13 +9895,13 @@
         <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>419</v>
+        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9925,10 +9912,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9948,23 +9935,21 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>183</v>
+        <v>546</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>549</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -9988,13 +9973,13 @@
         <v>84</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>531</v>
+        <v>84</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>84</v>
@@ -10012,7 +9997,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10036,13 +10021,13 @@
         <v>84</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>523</v>
+        <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>419</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10053,10 +10038,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10067,7 +10052,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10076,20 +10061,22 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>533</v>
+        <v>486</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10138,13 +10125,13 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>84</v>
@@ -10165,10 +10152,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>84</v>
+        <v>556</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10179,10 +10166,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10208,10 +10195,10 @@
         <v>161</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>539</v>
+        <v>162</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>540</v>
+        <v>163</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10262,7 +10249,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>538</v>
+        <v>164</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10274,7 +10261,7 @@
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10289,10 +10276,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>541</v>
+        <v>165</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10303,14 +10290,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>542</v>
+        <v>559</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10326,19 +10313,19 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>543</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>544</v>
+        <v>141</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>545</v>
+        <v>167</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>546</v>
+        <v>143</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10388,7 +10375,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>542</v>
+        <v>171</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10400,7 +10387,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10415,10 +10402,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>548</v>
+        <v>165</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10429,14 +10416,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10449,24 +10436,26 @@
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>550</v>
+        <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>551</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>552</v>
+        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10514,7 +10503,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>549</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10526,7 +10515,7 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10541,10 +10530,10 @@
         <v>84</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>547</v>
+        <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>554</v>
+        <v>137</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10555,10 +10544,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10566,10 +10555,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10581,19 +10570,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>490</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>559</v>
+        <v>278</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10618,13 +10607,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10642,13 +10631,13 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
@@ -10666,16 +10655,16 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>560</v>
+        <v>284</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>561</v>
+        <v>285</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>84</v>
+        <v>286</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10683,10 +10672,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10706,19 +10695,23 @@
         <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>161</v>
+        <v>569</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>162</v>
+        <v>570</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>359</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10766,7 +10759,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>164</v>
+        <v>568</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10778,7 +10771,7 @@
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
@@ -10790,38 +10783,38 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>84</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>165</v>
+        <v>363</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>84</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10833,18 +10826,20 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>141</v>
+        <v>574</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>167</v>
+        <v>575</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>576</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>400</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10868,13 +10863,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>401</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>402</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10892,19 +10887,19 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>171</v>
+        <v>573</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>84</v>
@@ -10919,10 +10914,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>165</v>
+        <v>404</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10933,14 +10928,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10953,25 +10948,25 @@
         <v>84</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>502</v>
+        <v>407</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>503</v>
+        <v>408</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>149</v>
+        <v>410</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10996,13 +10991,13 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11020,7 +11015,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>504</v>
+        <v>577</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11032,7 +11027,7 @@
         <v>84</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>84</v>
@@ -11044,27 +11039,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>84</v>
+        <v>414</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>137</v>
+        <v>415</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>84</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11072,10 +11067,10 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11084,22 +11079,22 @@
         <v>84</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>183</v>
+        <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>568</v>
+        <v>489</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>278</v>
+        <v>490</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11124,13 +11119,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11148,13 +11143,13 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
@@ -11172,535 +11167,23 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>571</v>
+        <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>282</v>
+        <v>492</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>283</v>
+        <v>493</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>284</v>
+        <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="P73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR75">
+  <autoFilter ref="A1:AR71">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11710,7 +11193,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI74">
+  <conditionalFormatting sqref="A2:AI70">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="580">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1237,13 +1237,10 @@
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
   </si>
   <si>
-    <t>[HEALTH FACTOR]</t>
-  </si>
-  <si>
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: fixed value = [HEALTH FACTOR]</t>
+    <t>1249-1: undefined</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -6932,46 +6929,46 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="T38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6986,22 +6983,22 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7012,10 +7009,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7041,16 +7038,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7078,11 +7075,11 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7099,7 +7096,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7108,7 +7105,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7129,7 +7126,7 @@
         <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7140,14 +7137,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7169,16 +7166,16 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7206,11 +7203,11 @@
         <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7227,7 +7224,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7251,27 +7248,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7294,19 +7291,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7355,7 +7352,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7382,10 +7379,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7396,10 +7393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7520,10 +7517,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7646,10 +7643,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7672,16 +7669,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7731,7 +7728,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7761,7 +7758,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7772,10 +7769,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7801,10 +7798,10 @@
         <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7855,7 +7852,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7885,7 +7882,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7896,10 +7893,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7922,13 +7919,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7979,7 +7976,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -7994,10 +7991,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8009,7 +8006,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8020,10 +8017,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8049,13 +8046,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8081,14 +8078,14 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Y47" t="s" s="2">
+      <c r="Z47" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8105,7 +8102,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8129,27 +8126,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8175,16 +8172,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8209,14 +8206,14 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8233,7 +8230,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8260,10 +8257,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8274,10 +8271,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8300,16 +8297,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8359,7 +8356,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8383,27 +8380,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8426,16 +8423,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8485,7 +8482,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8509,27 +8506,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8552,19 +8549,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8613,7 +8610,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8625,25 +8622,25 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AK51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8654,10 +8651,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8778,10 +8775,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8904,14 +8901,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8933,10 +8930,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8991,7 +8988,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9032,10 +9029,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9058,13 +9055,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9115,7 +9112,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9124,7 +9121,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9142,10 +9139,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9156,10 +9153,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9182,13 +9179,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9239,7 +9236,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9248,7 +9245,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9266,10 +9263,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9280,10 +9277,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9309,16 +9306,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9346,11 +9343,11 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9367,7 +9364,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9391,13 +9388,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AP57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9408,10 +9405,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9437,16 +9434,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9471,14 +9468,14 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9495,7 +9492,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9519,13 +9516,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9536,10 +9533,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9562,17 +9559,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9621,7 +9618,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9651,7 +9648,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9662,10 +9659,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9691,10 +9688,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9745,7 +9742,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9772,10 +9769,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9786,10 +9783,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9812,16 +9809,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9871,7 +9868,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9898,10 +9895,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9912,10 +9909,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9938,16 +9935,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9997,7 +9994,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10024,10 +10021,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10038,10 +10035,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10064,19 +10061,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10125,7 +10122,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10152,10 +10149,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10166,10 +10163,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10290,10 +10287,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10416,14 +10413,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10445,10 +10442,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10503,7 +10500,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10544,10 +10541,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10573,13 +10570,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>278</v>
@@ -10607,14 +10604,14 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10631,7 +10628,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10655,7 +10652,7 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>284</v>
@@ -10672,10 +10669,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10698,16 +10695,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>357</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>359</v>
@@ -10759,7 +10756,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10783,7 +10780,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>362</v>
@@ -10800,10 +10797,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10829,16 +10826,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10866,11 +10863,11 @@
         <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10887,7 +10884,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10896,7 +10893,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10917,7 +10914,7 @@
         <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10928,14 +10925,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10957,16 +10954,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10994,11 +10991,11 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11015,7 +11012,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11039,27 +11036,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11085,16 +11082,16 @@
         <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11143,7 +11140,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11170,10 +11167,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1095,7 +1095,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1240,7 +1240,10 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: undefined</t>
+    <t>1249-1: source value from V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01-.01)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -6986,7 +6989,7 @@
         <v>392</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>84</v>
@@ -6995,10 +6998,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7009,10 +7012,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7038,16 +7041,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7075,10 +7078,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7096,7 +7099,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7105,7 +7108,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7126,7 +7129,7 @@
         <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7137,14 +7140,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7166,16 +7169,16 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7203,10 +7206,10 @@
         <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7224,7 +7227,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7248,27 +7251,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7291,19 +7294,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7352,7 +7355,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7379,10 +7382,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7393,10 +7396,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7517,10 +7520,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7643,10 +7646,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7669,16 +7672,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7728,7 +7731,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7758,7 +7761,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7769,10 +7772,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7798,10 +7801,10 @@
         <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7852,7 +7855,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7882,7 +7885,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7893,10 +7896,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7919,13 +7922,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7976,7 +7979,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -7991,10 +7994,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8006,7 +8009,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8017,10 +8020,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8046,13 +8049,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8078,13 +8081,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8102,7 +8105,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8126,27 +8129,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8172,16 +8175,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8206,13 +8209,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8230,7 +8233,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8257,10 +8260,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8271,10 +8274,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8297,16 +8300,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8356,7 +8359,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8380,27 +8383,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8423,16 +8426,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8482,7 +8485,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8506,27 +8509,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8549,19 +8552,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8610,7 +8613,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8622,7 +8625,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8637,10 +8640,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8651,10 +8654,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8775,10 +8778,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8901,14 +8904,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8930,10 +8933,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8988,7 +8991,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9029,10 +9032,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9055,13 +9058,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9112,7 +9115,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9121,7 +9124,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9139,10 +9142,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9153,10 +9156,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9179,13 +9182,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9236,7 +9239,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9245,7 +9248,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9263,10 +9266,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9277,10 +9280,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9306,16 +9309,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9343,10 +9346,10 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9364,7 +9367,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9388,13 +9391,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9405,10 +9408,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9434,16 +9437,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9468,13 +9471,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9492,7 +9495,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9516,13 +9519,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9533,10 +9536,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9559,17 +9562,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9618,7 +9621,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9648,7 +9651,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9659,10 +9662,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9688,10 +9691,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9742,7 +9745,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9769,10 +9772,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9783,10 +9786,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9809,16 +9812,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9868,7 +9871,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9895,10 +9898,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9909,10 +9912,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9935,16 +9938,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9994,7 +9997,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10021,10 +10024,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10035,10 +10038,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10061,19 +10064,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10122,7 +10125,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10149,10 +10152,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10163,10 +10166,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10287,10 +10290,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10413,14 +10416,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10442,10 +10445,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10500,7 +10503,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10541,10 +10544,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10570,13 +10573,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>278</v>
@@ -10604,13 +10607,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10628,7 +10631,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10652,7 +10655,7 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>284</v>
@@ -10669,10 +10672,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10695,16 +10698,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>357</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>359</v>
@@ -10756,7 +10759,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10780,7 +10783,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>362</v>
@@ -10797,10 +10800,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10826,16 +10829,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10863,10 +10866,10 @@
         <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10884,7 +10887,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10893,7 +10896,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10914,7 +10917,7 @@
         <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10925,14 +10928,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10954,16 +10957,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10991,10 +10994,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11012,7 +11015,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11036,27 +11039,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11082,16 +11085,16 @@
         <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11140,7 +11143,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11167,10 +11170,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="580">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1240,10 +1240,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: source value from V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01-.01)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
+    <t>1249-1: undefined</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -6989,19 +6986,19 @@
         <v>392</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7012,10 +7009,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7041,16 +7038,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7078,11 +7075,11 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7099,7 +7096,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7108,7 +7105,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7129,7 +7126,7 @@
         <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7140,14 +7137,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7169,16 +7166,16 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7206,11 +7203,11 @@
         <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7227,7 +7224,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7251,27 +7248,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO40" t="s" s="2">
+      <c r="AP40" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR40" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AQ40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7294,19 +7291,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7355,7 +7352,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7382,10 +7379,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7396,10 +7393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7520,10 +7517,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7646,10 +7643,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7672,16 +7669,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7731,7 +7728,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7761,7 +7758,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7772,10 +7769,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7801,10 +7798,10 @@
         <v>321</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7855,7 +7852,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7885,7 +7882,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7896,10 +7893,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7922,13 +7919,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7979,7 +7976,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -7994,10 +7991,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8009,7 +8006,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8020,10 +8017,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8049,13 +8046,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8081,14 +8078,14 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="Y47" t="s" s="2">
+      <c r="Z47" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8105,7 +8102,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8129,27 +8126,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="AP47" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR47" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8175,16 +8172,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8209,14 +8206,14 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8233,7 +8230,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8260,10 +8257,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8274,10 +8271,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8300,16 +8297,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8359,7 +8356,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8383,27 +8380,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AO49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8426,16 +8423,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8485,7 +8482,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8509,27 +8506,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR50" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8552,19 +8549,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8613,7 +8610,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8625,25 +8622,25 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO51" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AK51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP51" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8654,10 +8651,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8778,10 +8775,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8904,14 +8901,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8933,10 +8930,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8991,7 +8988,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9032,10 +9029,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9058,13 +9055,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9115,7 +9112,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9124,7 +9121,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9142,10 +9139,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AP55" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9156,10 +9153,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9182,13 +9179,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9239,7 +9236,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9248,7 +9245,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9266,10 +9263,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9280,10 +9277,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9309,16 +9306,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9346,11 +9343,11 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>518</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9367,7 +9364,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9391,13 +9388,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AO57" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AP57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9408,10 +9405,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9437,16 +9434,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9471,14 +9468,14 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
       </c>
@@ -9495,7 +9492,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9519,13 +9516,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>519</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>520</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9536,10 +9533,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9562,17 +9559,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>531</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9621,7 +9618,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9651,7 +9648,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9662,10 +9659,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9691,10 +9688,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>536</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9745,7 +9742,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9772,10 +9769,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9786,10 +9783,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9812,16 +9809,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9871,7 +9868,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9898,10 +9895,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9912,10 +9909,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9938,16 +9935,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>546</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9997,7 +9994,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10024,10 +10021,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10038,10 +10035,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10064,19 +10061,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10125,7 +10122,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10152,10 +10149,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10166,10 +10163,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10290,10 +10287,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10416,14 +10413,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10445,10 +10442,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10503,7 +10500,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10544,10 +10541,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10573,13 +10570,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>278</v>
@@ -10607,14 +10604,14 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>566</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10631,7 +10628,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10655,7 +10652,7 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>284</v>
@@ -10672,10 +10669,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10698,16 +10695,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>357</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>359</v>
@@ -10759,7 +10756,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10783,7 +10780,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>362</v>
@@ -10800,10 +10797,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10829,16 +10826,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10866,11 +10863,11 @@
         <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
       </c>
@@ -10887,7 +10884,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10896,7 +10893,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10917,7 +10914,7 @@
         <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10928,14 +10925,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10957,16 +10954,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10994,11 +10991,11 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>412</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
       </c>
@@ -11015,7 +11012,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11039,27 +11036,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AP70" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11085,16 +11082,16 @@
         <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="N71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>489</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>490</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11143,7 +11140,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11170,10 +11167,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AP71" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1166,7 +1166,7 @@
     <t>Coded Responses from Smoking Status Value Set</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFSmokingStatus</t>
+    <t>http://va.gov/fhir/ValueSet/SmokingStatus</t>
   </si>
   <si>
     <t>1249: terminologyMaps using VF_SmokingStatus on V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01)</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2897" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -889,6 +889,10 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-smoking-status-observation-codes</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+SmokingStatusObservation-1244:if TOBACCO [C] then fixed value http://loinc.org#72166-2 {null}</t>
   </si>
   <si>
     <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>
@@ -5330,39 +5334,39 @@
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>280</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5385,19 +5389,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5446,7 +5450,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5461,25 +5465,25 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -5487,10 +5491,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5513,16 +5517,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5572,7 +5576,7 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5599,13 +5603,13 @@
         <v>84</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR27" t="s" s="2">
         <v>84</v>
@@ -5613,14 +5617,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5639,19 +5643,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5700,7 +5704,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5715,25 +5719,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5741,14 +5745,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5767,19 +5771,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5816,17 +5820,17 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5847,19 +5851,19 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR29" t="s" s="2">
         <v>84</v>
@@ -5867,16 +5871,16 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5895,19 +5899,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5956,7 +5960,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5971,25 +5975,25 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AR30" t="s" s="2">
         <v>84</v>
@@ -5997,10 +6001,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6023,16 +6027,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6082,7 +6086,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6109,13 +6113,13 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>84</v>
@@ -6123,10 +6127,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6149,17 +6153,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6208,7 +6212,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6223,25 +6227,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6249,10 +6253,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6278,16 +6282,16 @@
         <v>183</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6324,17 +6328,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6343,7 +6347,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -6358,30 +6362,30 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -6406,16 +6410,16 @@
         <v>183</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6444,7 +6448,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -6462,7 +6466,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6471,42 +6475,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6627,10 +6631,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6753,10 +6757,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6779,19 +6783,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -6840,7 +6844,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6867,10 +6871,10 @@
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6881,10 +6885,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6910,16 +6914,16 @@
         <v>161</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6968,7 +6972,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6983,7 +6987,7 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>84</v>
@@ -6995,10 +6999,10 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7009,10 +7013,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7038,16 +7042,16 @@
         <v>183</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7075,10 +7079,10 @@
         <v>188</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>84</v>
@@ -7096,7 +7100,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7105,7 +7109,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -7126,7 +7130,7 @@
         <v>137</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -7137,14 +7141,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7166,16 +7170,16 @@
         <v>183</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7203,10 +7207,10 @@
         <v>188</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>84</v>
@@ -7224,7 +7228,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7248,27 +7252,27 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7291,19 +7295,19 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7352,7 +7356,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7379,10 +7383,10 @@
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7393,10 +7397,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7517,10 +7521,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7643,10 +7647,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7669,16 +7673,16 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7728,7 +7732,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7758,7 +7762,7 @@
         <v>137</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7769,10 +7773,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7795,13 +7799,13 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7852,7 +7856,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7882,7 +7886,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7893,10 +7897,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7919,13 +7923,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7976,7 +7980,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>94</v>
@@ -7991,10 +7995,10 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>84</v>
@@ -8006,7 +8010,7 @@
         <v>137</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8017,10 +8021,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8046,13 +8050,13 @@
         <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8078,13 +8082,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8102,7 +8106,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8126,27 +8130,27 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8172,16 +8176,16 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8206,13 +8210,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8230,7 +8234,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8257,10 +8261,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8271,10 +8275,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8297,16 +8301,16 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8356,7 +8360,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8380,27 +8384,27 @@
         <v>84</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8423,16 +8427,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8482,7 +8486,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8506,27 +8510,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8549,19 +8553,19 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8610,7 +8614,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8622,7 +8626,7 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -8637,10 +8641,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8651,10 +8655,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8775,10 +8779,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8901,14 +8905,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8930,10 +8934,10 @@
         <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8988,7 +8992,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9029,10 +9033,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9055,13 +9059,13 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9112,7 +9116,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9121,7 +9125,7 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -9139,10 +9143,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9153,10 +9157,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9179,13 +9183,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9236,7 +9240,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9245,7 +9249,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9263,10 +9267,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9277,10 +9281,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9306,16 +9310,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9343,10 +9347,10 @@
         <v>118</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9364,7 +9368,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9388,13 +9392,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9405,10 +9409,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9434,16 +9438,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9468,13 +9472,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9492,7 +9496,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9516,13 +9520,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9533,10 +9537,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9559,17 +9563,17 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9618,7 +9622,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9648,7 +9652,7 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9659,10 +9663,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9688,10 +9692,10 @@
         <v>161</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9742,7 +9746,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9769,10 +9773,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9783,10 +9787,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9809,16 +9813,16 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9868,7 +9872,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -9895,10 +9899,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -9909,10 +9913,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9935,16 +9939,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9994,7 +9998,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10021,10 +10025,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10035,10 +10039,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10061,19 +10065,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10122,7 +10126,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10149,10 +10153,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10163,10 +10167,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10287,10 +10291,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10413,14 +10417,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10442,10 +10446,10 @@
         <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>143</v>
@@ -10500,7 +10504,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10541,10 +10545,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10570,13 +10574,13 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>278</v>
@@ -10604,13 +10608,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10628,7 +10632,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>94</v>
@@ -10652,16 +10656,16 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -10669,10 +10673,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10695,19 +10699,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10756,7 +10760,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10780,27 +10784,27 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10826,16 +10830,16 @@
         <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10863,10 +10867,10 @@
         <v>188</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10884,7 +10888,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -10893,7 +10897,7 @@
         <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>106</v>
@@ -10914,7 +10918,7 @@
         <v>137</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -10925,14 +10929,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10954,16 +10958,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -10991,10 +10995,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11012,7 +11016,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11036,27 +11040,27 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11082,16 +11086,16 @@
         <v>85</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11140,7 +11144,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11167,10 +11171,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -892,7 +892,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-SmokingStatusObservation-1244:if TOBACCO [C] then fixed value http://loinc.org#72166-2 {null}</t>
+sso-24-1244:9000010.23-.01 &gt; 9999999.64-.03: if TOBACCO [C] then http://loinc.org#72166-2 {null}</t>
   </si>
   <si>
     <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="588">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -905,7 +905,7 @@
 Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
   </si>
   <si>
-    <t>healthFactor.category,healthFactor.name</t>
+    <t>Vaccination.OrderItem,SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.SocialHistoryExtension.Category,SocialHistory.SocialHistoryExtension.QuantityLabel,SocialHistory.SocialHabitCategory.Description,FamilyHistory.Diagnosis,FamilyHistory.FamilyHistoryExtension.Category,FamilyHistory.Diagnosis.Description</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1011,7 +1011,7 @@
     <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
   </si>
   <si>
-    <t>healthFactor.encounter,healthFactor.facility,healthFactor.recorded</t>
+    <t>Vaccination.EncounterNumber,Vaccination.EnteredAt,Vaccination.EnteredBy,Vaccination.EnteredOn,Vaccination.Administration.AdministeredAtLocation,SocialHistory.EncounterNumber,SocialHistory.EnteredAt,SocialHistory.EnteredBy,SocialHistory.EnteredOn,FamilyHistory.EncounterNumber,FamilyHistory.EnteredAt,FamilyHistory.EnteredBy,FamilyHistory.EnteredOn</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1080,6 +1080,9 @@
     <t>HF.HealthFactor.EventDateTime</t>
   </si>
   <si>
+    <t>Vaccination.FromTime,Vaccination.ToTime,SocialHistory.FromTime,FamilyHistory.FromTime</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1127,6 +1130,9 @@
     <t>HF.HealthFactor.EncounterStaffIEN</t>
   </si>
   <si>
+    <t>Vaccination.Administration.AdministeringProvider</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1189,6 +1195,10 @@
 Dim.HealthFactorType.HealthFactorCategory,Dim.HealthFactorType.HealthFactorType</t>
   </si>
   <si>
+    <t>Vaccination.OrderItem,SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.SocialHistoryExtension.Category,SocialHistory.SocialHistoryExtension.QuantityLabel,SocialHistory.SocialHabitCategory.Description,FamilyHistory.Diagnosis,FamilyHistory.FamilyHistoryExtension.Category,FamilyHistory.Diagnosis.Description
+Vaccination.Order.Description</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
@@ -1418,7 +1428,7 @@
     <t>HF.HealthFactor.Comments</t>
   </si>
   <si>
-    <t>healthFactor.comment</t>
+    <t>Vaccination.Administration.RefusalReason,SocialHistory.SocialHabitComments,FamilyHistory.NoteText</t>
   </si>
   <si>
     <t>Act.text</t>
@@ -2201,7 +2211,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="166.92578125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="80.4375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="62.3828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -6081,7 +6091,7 @@
         <v>339</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>85</v>
+        <v>340</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>332</v>
@@ -6104,10 +6114,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6130,16 +6140,16 @@
         <v>96</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6189,7 +6199,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6219,13 +6229,13 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AS31" t="s" s="2">
         <v>85</v>
@@ -6233,10 +6243,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6259,17 +6269,17 @@
         <v>96</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>85</v>
@@ -6318,7 +6328,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6333,28 +6343,28 @@
         <v>107</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AS32" t="s" s="2">
         <v>85</v>
@@ -6362,10 +6372,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6391,16 +6401,16 @@
         <v>184</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6447,7 +6457,7 @@
         <v>331</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6456,7 +6466,7 @@
         <v>95</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>107</v>
@@ -6474,30 +6484,30 @@
         <v>85</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS33" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>85</v>
@@ -6522,16 +6532,16 @@
         <v>184</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6560,7 +6570,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -6578,7 +6588,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6587,45 +6597,45 @@
         <v>95</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>284</v>
+        <v>377</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6749,10 +6759,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6878,10 +6888,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6904,19 +6914,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6965,7 +6975,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -6995,10 +7005,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -7009,10 +7019,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7038,16 +7048,16 @@
         <v>162</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>85</v>
@@ -7096,7 +7106,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7111,7 +7121,7 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>85</v>
@@ -7126,10 +7136,10 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
@@ -7140,10 +7150,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7169,16 +7179,16 @@
         <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7206,10 +7216,10 @@
         <v>189</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
@@ -7227,7 +7237,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7236,7 +7246,7 @@
         <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>107</v>
@@ -7260,7 +7270,7 @@
         <v>138</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7271,14 +7281,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7300,16 +7310,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7337,10 +7347,10 @@
         <v>189</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7358,7 +7368,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7385,27 +7395,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7428,19 +7438,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7489,7 +7499,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7519,10 +7529,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7533,10 +7543,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7660,10 +7670,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7789,10 +7799,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7815,16 +7825,16 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7874,7 +7884,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7907,7 +7917,7 @@
         <v>138</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7918,10 +7928,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7947,10 +7957,10 @@
         <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8001,7 +8011,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8034,7 +8044,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8045,10 +8055,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8071,13 +8081,13 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8128,7 +8138,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8143,13 +8153,13 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>85</v>
@@ -8161,7 +8171,7 @@
         <v>138</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -8172,10 +8182,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8201,13 +8211,13 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8233,13 +8243,13 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8257,7 +8267,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8284,27 +8294,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8330,16 +8340,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8364,13 +8374,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8388,7 +8398,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8418,10 +8428,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8432,10 +8442,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8458,16 +8468,16 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8517,7 +8527,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8544,27 +8554,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8587,16 +8597,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8646,7 +8656,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8673,27 +8683,27 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8716,19 +8726,19 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8777,7 +8787,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8789,7 +8799,7 @@
         <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>85</v>
@@ -8807,10 +8817,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8821,10 +8831,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8948,10 +8958,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9077,14 +9087,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9106,10 +9116,10 @@
         <v>141</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>144</v>
@@ -9164,7 +9174,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9208,10 +9218,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9234,13 +9244,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9291,7 +9301,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9300,7 +9310,7 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>107</v>
@@ -9321,10 +9331,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9335,10 +9345,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9361,13 +9371,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9418,7 +9428,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9427,7 +9437,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9448,10 +9458,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9462,10 +9472,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9491,16 +9501,16 @@
         <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9528,10 +9538,10 @@
         <v>119</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9549,7 +9559,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9576,13 +9586,13 @@
         <v>85</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9593,10 +9603,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9622,16 +9632,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9656,13 +9666,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9680,7 +9690,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9707,13 +9717,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9724,10 +9734,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9750,17 +9760,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9809,7 +9819,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9842,7 +9852,7 @@
         <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9853,10 +9863,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9882,10 +9892,10 @@
         <v>162</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9936,7 +9946,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9966,10 +9976,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -9980,10 +9990,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10006,16 +10016,16 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10065,7 +10075,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10095,10 +10105,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10109,10 +10119,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10135,16 +10145,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10194,7 +10204,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10224,10 +10234,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10238,10 +10248,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10264,19 +10274,19 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10325,7 +10335,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10355,10 +10365,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10369,10 +10379,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10496,10 +10506,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10625,14 +10635,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10654,10 +10664,10 @@
         <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>144</v>
@@ -10712,7 +10722,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10756,10 +10766,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10785,13 +10795,13 @@
         <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>279</v>
@@ -10819,13 +10829,13 @@
         <v>85</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>85</v>
@@ -10843,7 +10853,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>95</v>
@@ -10870,7 +10880,7 @@
         <v>85</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>287</v>
@@ -10887,10 +10897,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10913,19 +10923,19 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -10974,7 +10984,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11001,27 +11011,27 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11047,16 +11057,16 @@
         <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11084,10 +11094,10 @@
         <v>189</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11105,7 +11115,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11114,7 +11124,7 @@
         <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
@@ -11138,7 +11148,7 @@
         <v>138</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11149,14 +11159,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11178,16 +11188,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11215,10 +11225,10 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11236,7 +11246,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11263,27 +11273,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11309,16 +11319,16 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11367,7 +11377,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11397,10 +11407,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -905,7 +905,7 @@
 Dim.HealthFactorType.CategoryHealthFactorTypeIEN</t>
   </si>
   <si>
-    <t>Vaccination.OrderItem,SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.SocialHistoryExtension.Category,SocialHistory.SocialHistoryExtension.QuantityLabel,SocialHistory.SocialHabitCategory.Description,FamilyHistory.Diagnosis,FamilyHistory.FamilyHistoryExtension.Category,FamilyHistory.Diagnosis.Description</t>
+    <t>SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.Extension[SocialHistoryExtension].Category,SocialHistory.Extension[SocialHistoryExtension].QuantityLabel,SocialHistory.SocialHabitCategory.Description,Vaccination.OrderItem,FamilyHistory.Diagnosis,FamilyHistory.Extension[FamilyHistoryExtension].Category,FamilyHistory.Diagnosis.Description</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1011,7 +1011,7 @@
     <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
   </si>
   <si>
-    <t>Vaccination.EncounterNumber,Vaccination.EnteredAt,Vaccination.EnteredBy,Vaccination.EnteredOn,Vaccination.Administration.AdministeredAtLocation,SocialHistory.EncounterNumber,SocialHistory.EnteredAt,SocialHistory.EnteredBy,SocialHistory.EnteredOn,FamilyHistory.EncounterNumber,FamilyHistory.EnteredAt,FamilyHistory.EnteredBy,FamilyHistory.EnteredOn</t>
+    <t>SocialHistory.EncounterNumber,SocialHistory.EnteredAt,SocialHistory.EnteredBy,SocialHistory.EnteredOn,Vaccination.EncounterNumber,Vaccination.EnteredAt,Vaccination.EnteredBy,Vaccination.EnteredOn,Vaccination.Administration.AdministeredAtLocation,FamilyHistory.EncounterNumber,FamilyHistory.EnteredAt,FamilyHistory.EnteredBy,FamilyHistory.EnteredOn</t>
   </si>
   <si>
     <t>Event.context</t>
@@ -1080,7 +1080,7 @@
     <t>HF.HealthFactor.EventDateTime</t>
   </si>
   <si>
-    <t>Vaccination.FromTime,Vaccination.ToTime,SocialHistory.FromTime,FamilyHistory.FromTime</t>
+    <t>SocialHistory.FromTime,Vaccination.FromTime,Vaccination.ToTime,FamilyHistory.FromTime</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1195,8 +1195,8 @@
 Dim.HealthFactorType.HealthFactorCategory,Dim.HealthFactorType.HealthFactorType</t>
   </si>
   <si>
-    <t>Vaccination.OrderItem,SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.SocialHistoryExtension.Category,SocialHistory.SocialHistoryExtension.QuantityLabel,SocialHistory.SocialHabitCategory.Description,FamilyHistory.Diagnosis,FamilyHistory.FamilyHistoryExtension.Category,FamilyHistory.Diagnosis.Description
-Vaccination.Order.Description</t>
+    <t>SocialHistory.SocialHabit,SocialHistory.SocialHabitCategory,SocialHistory.Extension[SocialHistoryExtension].Category,SocialHistory.Extension[SocialHistoryExtension].QuantityLabel,SocialHistory.SocialHabitCategory.Description,Vaccination.OrderItem,FamilyHistory.Diagnosis,FamilyHistory.Extension[FamilyHistoryExtension].Category,FamilyHistory.Diagnosis.Description
+Vaccination.OrderItem[Order].Description</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
@@ -1428,7 +1428,7 @@
     <t>HF.HealthFactor.Comments</t>
   </si>
   <si>
-    <t>Vaccination.Administration.RefusalReason,SocialHistory.SocialHabitComments,FamilyHistory.NoteText</t>
+    <t>SocialHistory.SocialHabitComments,Vaccination.Administration.RefusalReason,FamilyHistory.NoteText</t>
   </si>
   <si>
     <t>Act.text</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file V HEALTH FACTORS (9000010.23) to us-core-smokingstatus</t>
+    <t>This StructureDefinition contains the maps for VistA file V HEALTH FACTORS (9000010.23) to us-core-smokingstatus.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1241: source value from V HEALTH FACTORS - IEN (9000010.23-.001)</t>
+    <t>1241: source value based on V HEALTH FACTORS - IEN (9000010.23-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -895,10 +895,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-sso-24-1244:9000010.23-.01 &gt; 9999999.64-.03: if TOBACCO [C] then http://loinc.org#72166-2 {null}</t>
-  </si>
-  <si>
-    <t>1244: fixed value = http://loinc.org#72166-2 when V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - CATEGORY (9000010.23-.01 &gt; 9999999.64-.03) case TOBACCO [C]</t>
+sso-24-1244:If (9000010.23-.01 &gt; 9999999.64-.03) is TOBACCO [C] then fixed value http://loinc.org#72166-2 {null}sso-24-1862:If (9000010.23-.01 &gt; 9999999.64-.03) is Not TOBACCO [C] then exclude record {null}</t>
+  </si>
+  <si>
+    <t>1862: exclude record if Not TOBACCO [C]</t>
   </si>
   <si>
     <t>HF.HealthFactor.HealthFactorTypeIEN
@@ -945,7 +945,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1245: reference from V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
+    <t>1245: reference based on V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
   </si>
   <si>
     <t>HF.HealthFactor.PatientIEN</t>
@@ -1005,7 +1005,7 @@
     <t>For some observations it may be important to know the link between an observation and a particular encounter.</t>
   </si>
   <si>
-    <t>1246: reference from V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
+    <t>1246: reference based on V HEALTH FACTORS - VISIT (9000010.23-.03)</t>
   </si>
   <si>
     <t>HF.HealthFactor.VisitDateTime,HF.HealthFactor.VisitIEN</t>
@@ -1074,7 +1074,7 @@
     <t>effectiveDateTime</t>
   </si>
   <si>
-    <t>1247: source value from V HEALTH FACTORS - EVENT DATE AND TIME (9000010.23-1201)</t>
+    <t>1247: source value based on V HEALTH FACTORS - EVENT DATE AND TIME (9000010.23-1201)</t>
   </si>
   <si>
     <t>HF.HealthFactor.EventDateTime</t>
@@ -1124,7 +1124,7 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t>1248: reference from V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
+    <t>1248: reference based on V HEALTH FACTORS - ENCOUNTER PROVIDER (9000010.23-1204)</t>
   </si>
   <si>
     <t>HF.HealthFactor.EncounterStaffIEN</t>
@@ -1263,7 +1263,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: undefined</t>
+    <t>1249-1: source value</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -1422,7 +1422,7 @@
     <t>Annotation.text</t>
   </si>
   <si>
-    <t>1250: source value from V HEALTH FACTORS - COMMENTS (9000010.23-81101)</t>
+    <t>1250: source value based on V HEALTH FACTORS - COMMENTS (9000010.23-81101)</t>
   </si>
   <si>
     <t>HF.HealthFactor.Comments</t>
@@ -2209,7 +2209,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="166.92578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="147.328125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="80.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="590">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1185,6 +1185,9 @@
     <t>Coded Responses from Smoking Status Value Set</t>
   </si>
   <si>
+    <t>see mapping [VF_SmokingStatus](ConceptMap-VF-SmokingStatus.html)</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/SmokingStatus</t>
   </si>
   <si>
@@ -1263,7 +1266,10 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: source value</t>
+    <t>1249-1: source value based on V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01-.01)</t>
+  </si>
+  <si>
+    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -6568,9 +6574,11 @@
       <c r="X34" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y34" s="2"/>
+      <c r="Y34" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>85</v>
@@ -6603,13 +6611,13 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>85</v>
@@ -6632,10 +6640,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6759,10 +6767,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6888,10 +6896,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6914,19 +6922,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -6975,7 +6983,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7005,10 +7013,10 @@
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>85</v>
@@ -7019,10 +7027,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7048,16 +7056,16 @@
         <v>162</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>85</v>
@@ -7106,7 +7114,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7121,13 +7129,13 @@
         <v>107</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>85</v>
+        <v>401</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>85</v>
@@ -7136,10 +7144,10 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
@@ -7150,10 +7158,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7179,16 +7187,16 @@
         <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7216,10 +7224,10 @@
         <v>189</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
@@ -7237,7 +7245,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7246,7 +7254,7 @@
         <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>107</v>
@@ -7270,7 +7278,7 @@
         <v>138</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7281,14 +7289,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7310,16 +7318,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7347,10 +7355,10 @@
         <v>189</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
@@ -7368,7 +7376,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7395,27 +7403,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS40" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7438,19 +7446,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7499,7 +7507,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7529,10 +7537,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7543,10 +7551,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7670,10 +7678,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7799,10 +7807,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7825,16 +7833,16 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7884,7 +7892,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7917,7 +7925,7 @@
         <v>138</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7928,10 +7936,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7957,10 +7965,10 @@
         <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8011,7 +8019,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8044,7 +8052,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8055,10 +8063,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8081,13 +8089,13 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8138,7 +8146,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8153,13 +8161,13 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>85</v>
@@ -8171,7 +8179,7 @@
         <v>138</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -8182,10 +8190,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8211,13 +8219,13 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8243,13 +8251,13 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8267,7 +8275,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8294,27 +8302,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8340,16 +8348,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8374,13 +8382,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8398,7 +8406,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8428,10 +8436,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8442,10 +8450,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8468,16 +8476,16 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8527,7 +8535,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8554,27 +8562,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8597,16 +8605,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8656,7 +8664,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8683,27 +8691,27 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8726,19 +8734,19 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8787,7 +8795,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8799,7 +8807,7 @@
         <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>85</v>
@@ -8817,10 +8825,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8831,10 +8839,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8958,10 +8966,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9087,14 +9095,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9116,10 +9124,10 @@
         <v>141</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>144</v>
@@ -9174,7 +9182,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9218,10 +9226,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9244,13 +9252,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9301,7 +9309,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9310,7 +9318,7 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>107</v>
@@ -9331,10 +9339,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9345,10 +9353,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9371,13 +9379,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9428,7 +9436,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9437,7 +9445,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9458,10 +9466,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9472,10 +9480,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9501,16 +9509,16 @@
         <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9538,10 +9546,10 @@
         <v>119</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9559,7 +9567,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9586,13 +9594,13 @@
         <v>85</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9603,10 +9611,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9632,16 +9640,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9666,13 +9674,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9690,7 +9698,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9717,13 +9725,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9734,10 +9742,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9760,17 +9768,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9819,7 +9827,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9852,7 +9860,7 @@
         <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9863,10 +9871,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9892,10 +9900,10 @@
         <v>162</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9946,7 +9954,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9976,10 +9984,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -9990,10 +9998,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10016,16 +10024,16 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10075,7 +10083,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10105,10 +10113,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10119,10 +10127,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10145,16 +10153,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10204,7 +10212,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10234,10 +10242,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10248,10 +10256,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10274,19 +10282,19 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10335,7 +10343,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10365,10 +10373,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10379,10 +10387,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10506,10 +10514,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10635,14 +10643,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10664,10 +10672,10 @@
         <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>144</v>
@@ -10722,7 +10730,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10766,10 +10774,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10795,13 +10803,13 @@
         <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>279</v>
@@ -10829,13 +10837,13 @@
         <v>85</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>85</v>
@@ -10853,7 +10861,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>95</v>
@@ -10880,7 +10888,7 @@
         <v>85</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>287</v>
@@ -10897,10 +10905,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10923,16 +10931,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>363</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>365</v>
@@ -10984,7 +10992,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11011,7 +11019,7 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>368</v>
@@ -11028,10 +11036,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11057,16 +11065,16 @@
         <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11094,10 +11102,10 @@
         <v>189</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11115,7 +11123,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11124,7 +11132,7 @@
         <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
@@ -11148,7 +11156,7 @@
         <v>138</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11159,14 +11167,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11188,16 +11196,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11225,10 +11233,10 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11246,7 +11254,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11273,27 +11281,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS70" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11319,16 +11327,16 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11377,7 +11385,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11407,10 +11415,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2969" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1266,10 +1266,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1249-1: source value based on V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01-.01)</t>
-  </si>
-  <si>
-    <t>HF.HealthFactor.HealthFactorTypeIEN</t>
+    <t>1249-1: source value based on V HEALTH FACTORS - HEALTH FACTOR &gt; HEALTH FACTORS - FACTOR (9000010.23-.01 &gt; 9999999.64-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -7132,22 +7129,22 @@
         <v>400</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP38" t="s" s="2">
+      <c r="AQ38" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="AQ38" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>85</v>
@@ -7158,10 +7155,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7187,16 +7184,16 @@
         <v>184</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7224,11 +7221,11 @@
         <v>189</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>85</v>
       </c>
@@ -7245,7 +7242,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7254,7 +7251,7 @@
         <v>95</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>107</v>
@@ -7278,7 +7275,7 @@
         <v>138</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>85</v>
@@ -7289,14 +7286,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7318,16 +7315,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7355,11 +7352,11 @@
         <v>189</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z40" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>85</v>
       </c>
@@ -7376,7 +7373,7 @@
         <v>85</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7403,27 +7400,27 @@
         <v>85</v>
       </c>
       <c r="AO40" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AP40" t="s" s="2">
+      <c r="AQ40" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AQ40" t="s" s="2">
+      <c r="AR40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS40" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AR40" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7446,19 +7443,19 @@
         <v>85</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7507,7 +7504,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7537,10 +7534,10 @@
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AQ41" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>85</v>
@@ -7551,10 +7548,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7678,10 +7675,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7807,10 +7804,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7833,16 +7830,16 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7892,7 +7889,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -7925,7 +7922,7 @@
         <v>138</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
@@ -7936,10 +7933,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7965,10 +7962,10 @@
         <v>325</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -8019,7 +8016,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8052,7 +8049,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8063,10 +8060,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8089,13 +8086,13 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8146,7 +8143,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>95</v>
@@ -8161,13 +8158,13 @@
         <v>107</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>85</v>
@@ -8179,7 +8176,7 @@
         <v>138</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
@@ -8190,10 +8187,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8219,13 +8216,13 @@
         <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8251,14 +8248,14 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Y47" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Y47" t="s" s="2">
+      <c r="Z47" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8275,7 +8272,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8302,27 +8299,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AQ47" t="s" s="2">
+      <c r="AR47" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS47" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AR47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8348,16 +8345,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8382,14 +8379,14 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>473</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8406,7 +8403,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8436,10 +8433,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8450,10 +8447,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8476,16 +8473,16 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8535,7 +8532,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8562,27 +8559,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AQ49" t="s" s="2">
+      <c r="AR49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS49" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>484</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8605,16 +8602,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8664,7 +8661,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8691,27 +8688,27 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AP50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AQ50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS50" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>493</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8734,19 +8731,19 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -8795,7 +8792,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8807,28 +8804,28 @@
         <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="AK51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -8839,10 +8836,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8966,10 +8963,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9095,14 +9092,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9124,10 +9121,10 @@
         <v>141</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>144</v>
@@ -9182,7 +9179,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9226,10 +9223,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9252,13 +9249,13 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9309,7 +9306,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9318,7 +9315,7 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>107</v>
@@ -9339,10 +9336,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9353,10 +9350,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9379,13 +9376,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9436,7 +9433,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9445,7 +9442,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9466,10 +9463,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9480,10 +9477,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9509,16 +9506,16 @@
         <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9546,11 +9543,11 @@
         <v>119</v>
       </c>
       <c r="Y57" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="Z57" t="s" s="2">
         <v>526</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>527</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9567,7 +9564,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9594,13 +9591,13 @@
         <v>85</v>
       </c>
       <c r="AO57" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AP57" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AQ57" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9611,10 +9608,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9640,16 +9637,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9674,14 +9671,14 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>536</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9698,7 +9695,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9725,13 +9722,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="AP58" t="s" s="2">
-        <v>529</v>
-      </c>
       <c r="AQ58" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9742,10 +9739,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9768,17 +9765,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9827,7 +9824,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -9860,7 +9857,7 @@
         <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -9871,10 +9868,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9900,10 +9897,10 @@
         <v>162</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9954,7 +9951,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -9984,10 +9981,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -9998,10 +9995,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10024,16 +10021,16 @@
         <v>96</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10083,7 +10080,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10113,10 +10110,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10127,10 +10124,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10153,16 +10150,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10212,7 +10209,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10242,10 +10239,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10256,10 +10253,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10282,19 +10279,19 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>564</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10343,7 +10340,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10373,10 +10370,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AQ63" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10387,10 +10384,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10514,10 +10511,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10643,14 +10640,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10672,10 +10669,10 @@
         <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>144</v>
@@ -10730,7 +10727,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10774,10 +10771,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10803,13 +10800,13 @@
         <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="O67" t="s" s="2">
         <v>279</v>
@@ -10837,14 +10834,14 @@
         <v>85</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>85</v>
       </c>
@@ -10861,7 +10858,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>95</v>
@@ -10888,7 +10885,7 @@
         <v>85</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>287</v>
@@ -10905,10 +10902,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10931,16 +10928,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="M68" t="s" s="2">
         <v>363</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>365</v>
@@ -10992,7 +10989,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11019,7 +11016,7 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>368</v>
@@ -11036,10 +11033,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11065,16 +11062,16 @@
         <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="N69" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="O69" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11102,11 +11099,11 @@
         <v>189</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11123,7 +11120,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11132,7 +11129,7 @@
         <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
@@ -11156,7 +11153,7 @@
         <v>138</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11167,14 +11164,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11196,16 +11193,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11233,11 +11230,11 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11254,7 +11251,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11281,27 +11278,27 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AP70" t="s" s="2">
+      <c r="AQ70" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AQ70" t="s" s="2">
+      <c r="AR70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS70" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11327,16 +11324,16 @@
         <v>86</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="N71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="O71" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11385,7 +11382,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11415,10 +11412,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -895,7 +895,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-sso-24-1244:If (9000010.23-.01 &gt; 9999999.64-.03) is TOBACCO [C] then fixed value http://loinc.org#72166-2 {null}sso-24-1862:If (9000010.23-.01 &gt; 9999999.64-.03) is Not TOBACCO [C] then exclude record {null}</t>
+sso-24-1244:If (9000010.23-.01 &gt; 9999999.64-.03) is TOBACCO [C] then fixed value http://loinc.org#72166-2 {true}sso-24-1862:If (9000010.23-.01 &gt; 9999999.64-.03) is Not TOBACCO [C] then exclude record {true}</t>
   </si>
   <si>
     <t>1862: exclude record if Not TOBACCO [C]</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -945,7 +945,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>1245: reference based on V HEALTH FACTORS - PATIENT NAME (9000010.23-.02)</t>
+    <t>1245: reference based on V HEALTH FACTORS - PATIENT NAME &gt; PATIENT/IHS - NAME (9000010.23-.02 &gt; 9000001-.01)</t>
   </si>
   <si>
     <t>HF.HealthFactor.PatientIEN</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-SmokingStatusObservation.xlsx
+++ b/docs/StructureDefinition-SmokingStatusObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
